--- a/public/plantilla-indicadores.xlsx
+++ b/public/plantilla-indicadores.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="29">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,14 +71,6 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
@@ -170,14 +162,6 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="8.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
@@ -214,6 +198,44 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <sz val="7"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF1B2A45"/>
       <sz val="10"/>
     </font>
@@ -222,19 +244,66 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="8.5"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -246,18 +315,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
@@ -280,24 +337,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFEEF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
         <bgColor rgb="FFEEF1F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.0499893185216834"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCCF6A"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -427,19 +544,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -536,26 +640,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0"/>
       </left>
@@ -580,6 +664,327 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -600,13 +1005,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF9AA3B2"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF9AA3B2"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -619,321 +1024,911 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -943,7 +1938,154 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF595959"/>
+          <bgColor rgb="FF595959"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7F4F24"/>
+          <bgColor rgb="FF7F4F24"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF57C00"/>
+          <bgColor rgb="FFF57C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -957,14 +2099,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>2581275</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4937</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>10557</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -974,7 +2116,13 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="3024000" cy="1332000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1287,1987 +2435,1936 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="44" customWidth="1" style="70" min="1" max="1"/>
-    <col width="8.5" customWidth="1" style="70" min="2" max="2"/>
-    <col width="8.5" customWidth="1" style="70" min="3" max="3"/>
-    <col width="8.5" customWidth="1" style="70" min="4" max="4"/>
-    <col width="8.5" customWidth="1" style="70" min="5" max="5"/>
-    <col width="8.5" customWidth="1" style="70" min="6" max="6"/>
-    <col width="8.5" customWidth="1" style="70" min="7" max="7"/>
-    <col width="8.5" customWidth="1" style="70" min="8" max="8"/>
-    <col width="8.5" customWidth="1" style="70" min="9" max="9"/>
-    <col width="8.5" customWidth="1" style="70" min="10" max="10"/>
-    <col width="8.5" customWidth="1" style="70" min="11" max="11"/>
-    <col width="8.5" customWidth="1" style="70" min="12" max="12"/>
-    <col width="8.5" customWidth="1" style="70" min="13" max="13"/>
-    <col width="15" customWidth="1" style="70" min="14" max="14"/>
-    <col width="11" customWidth="1" style="70" min="15" max="15"/>
-    <col width="14" customWidth="1" style="70" min="16" max="16"/>
+    <col width="44" customWidth="1" style="127" min="1" max="1"/>
+    <col width="8.44140625" customWidth="1" style="127" min="2" max="13"/>
+    <col width="15" customWidth="1" style="127" min="14" max="14"/>
+    <col width="11" customWidth="1" style="127" min="15" max="15"/>
+    <col width="14" customWidth="1" style="127" min="16" max="16"/>
+    <col width="8.88671875" customWidth="1" style="127" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="70">
-      <c r="D1" s="35" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="127">
+      <c r="B1" s="220" t="inlineStr">
         <is>
           <t>INDICADORES DEL SG-SST</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" s="70">
-      <c r="D2" s="37" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-      <c r="M2" s="38" t="n"/>
-      <c r="N2" s="38" t="n"/>
-      <c r="O2" s="38" t="n"/>
-      <c r="P2" s="38" t="n"/>
-    </row>
-    <row r="3" ht="4.95" customHeight="1" s="70">
-      <c r="D3" s="75" t="n"/>
-      <c r="E3" s="56" t="n"/>
-      <c r="F3" s="56" t="n"/>
-      <c r="G3" s="56" t="n"/>
-      <c r="H3" s="56" t="n"/>
-      <c r="I3" s="56" t="n"/>
-      <c r="J3" s="56" t="n"/>
-      <c r="K3" s="56" t="n"/>
-      <c r="L3" s="56" t="n"/>
-      <c r="M3" s="56" t="n"/>
-      <c r="N3" s="56" t="n"/>
-      <c r="O3" s="56" t="n"/>
-      <c r="P3" s="56" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="70">
-      <c r="N4" s="53" t="inlineStr">
+    <row r="2" ht="14.4" customHeight="1" s="127"/>
+    <row r="3" ht="4.95" customHeight="1" s="127">
+      <c r="B3" s="225" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="127">
+      <c r="B4" s="92" t="n"/>
+      <c r="M4" s="92" t="n"/>
+      <c r="N4" s="139" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="31" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="70">
-      <c r="D5" s="40" t="inlineStr">
+      <c r="O4" s="93" t="n"/>
+      <c r="P4" s="89" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="127">
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="M5" s="41" t="n"/>
+      <c r="M5" s="92" t="n"/>
       <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="O5" s="49" t="inlineStr">
+      <c r="O5" s="64" t="inlineStr">
         <is>
           <t>RYR-SS-015</t>
         </is>
       </c>
-      <c r="P5" s="31" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="70">
-      <c r="D6" s="44" t="inlineStr">
+      <c r="P5" s="89" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="127">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="M6" s="41" t="n"/>
+      <c r="M6" s="92" t="n"/>
       <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="O6" s="49" t="n">
+      <c r="O6" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="P6" s="31" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="70">
-      <c r="D7" s="80" t="n"/>
-      <c r="E7" s="80" t="n"/>
-      <c r="F7" s="80" t="n"/>
-      <c r="G7" s="80" t="n"/>
-      <c r="H7" s="80" t="n"/>
-      <c r="I7" s="80" t="n"/>
-      <c r="J7" s="80" t="n"/>
-      <c r="K7" s="80" t="n"/>
-      <c r="L7" s="80" t="n"/>
-      <c r="M7" s="81" t="n"/>
+      <c r="P6" s="89" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="127">
+      <c r="B7" s="92" t="n"/>
+      <c r="M7" s="92" t="n"/>
       <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="O7" s="49" t="inlineStr">
+      <c r="O7" s="64" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="P7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="70">
-      <c r="D8" s="66" t="n"/>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="66" t="n"/>
-      <c r="H8" s="66" t="n"/>
-      <c r="I8" s="66" t="n"/>
-      <c r="J8" s="66" t="n"/>
-      <c r="K8" s="66" t="n"/>
-      <c r="L8" s="66" t="n"/>
-      <c r="M8" s="81" t="n"/>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="P7" s="89" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="127">
+      <c r="B8" s="92" t="n"/>
+      <c r="M8" s="92" t="n"/>
+      <c r="N8" s="254" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="O8" s="49" t="inlineStr">
+      <c r="O8" s="58" t="inlineStr">
         <is>
           <t>1 de 2</t>
         </is>
       </c>
-      <c r="P8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="70">
-      <c r="A9" s="103" t="inlineStr">
+      <c r="P8" s="94" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="127">
+      <c r="A9" s="255" t="inlineStr">
         <is>
           <t>Accidentalidad, salud y gestión del año · Resolución 0312 de 2019 · Decreto 1072 de 2015</t>
         </is>
       </c>
-      <c r="B9" s="115" t="n"/>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="115" t="n"/>
-      <c r="E9" s="115" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="115" t="n"/>
-      <c r="H9" s="115" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="115" t="n"/>
-      <c r="K9" s="115" t="n"/>
-      <c r="L9" s="115" t="n"/>
-      <c r="M9" s="115" t="n"/>
-      <c r="N9" s="115" t="n"/>
-      <c r="O9" s="115" t="n"/>
-      <c r="P9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="70">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="B9" s="349" t="n"/>
+      <c r="C9" s="349" t="n"/>
+      <c r="D9" s="349" t="n"/>
+      <c r="E9" s="349" t="n"/>
+      <c r="F9" s="349" t="n"/>
+      <c r="G9" s="349" t="n"/>
+      <c r="H9" s="349" t="n"/>
+      <c r="I9" s="349" t="n"/>
+      <c r="J9" s="349" t="n"/>
+      <c r="K9" s="349" t="n"/>
+      <c r="L9" s="349" t="n"/>
+      <c r="M9" s="349" t="n"/>
+      <c r="N9" s="349" t="n"/>
+      <c r="O9" s="349" t="n"/>
+      <c r="P9" s="351" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="127">
+      <c r="A10" s="137" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="38" t="n"/>
-      <c r="K10" s="38" t="n"/>
-      <c r="L10" s="38" t="n"/>
-      <c r="M10" s="38" t="n"/>
-      <c r="N10" s="38" t="n"/>
-      <c r="O10" s="38" t="n"/>
-      <c r="P10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="21" customHeight="1" s="70">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B10" s="98" t="n"/>
+      <c r="C10" s="98" t="n"/>
+      <c r="D10" s="98" t="n"/>
+      <c r="E10" s="98" t="n"/>
+      <c r="F10" s="98" t="n"/>
+      <c r="G10" s="98" t="n"/>
+      <c r="H10" s="98" t="n"/>
+      <c r="I10" s="98" t="n"/>
+      <c r="J10" s="98" t="n"/>
+      <c r="K10" s="98" t="n"/>
+      <c r="L10" s="98" t="n"/>
+      <c r="M10" s="98" t="n"/>
+      <c r="N10" s="98" t="n"/>
+      <c r="O10" s="98" t="n"/>
+      <c r="P10" s="97" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" s="127">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="50" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="31" t="n"/>
-      <c r="J11" s="33" t="inlineStr">
+      <c r="B11" s="161" t="n"/>
+      <c r="C11" s="93" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="93" t="n"/>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="89" t="n"/>
+      <c r="J11" s="59" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="31" t="n"/>
-      <c r="M11" s="48" t="n"/>
-      <c r="N11" s="30" t="n"/>
-      <c r="O11" s="30" t="n"/>
-      <c r="P11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="21" customHeight="1" s="70">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="K11" s="93" t="n"/>
+      <c r="L11" s="89" t="n"/>
+      <c r="M11" s="69" t="n"/>
+      <c r="N11" s="93" t="n"/>
+      <c r="O11" s="93" t="n"/>
+      <c r="P11" s="89" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" s="127">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="B12" s="43" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="30" t="n"/>
-      <c r="I12" s="31" t="n"/>
-      <c r="J12" s="33" t="inlineStr">
+      <c r="B12" s="68" t="n"/>
+      <c r="C12" s="93" t="n"/>
+      <c r="D12" s="93" t="n"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="F12" s="93" t="n"/>
+      <c r="G12" s="93" t="n"/>
+      <c r="H12" s="93" t="n"/>
+      <c r="I12" s="89" t="n"/>
+      <c r="J12" s="59" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="31" t="n"/>
-      <c r="M12" s="43" t="n"/>
-      <c r="N12" s="30" t="n"/>
-      <c r="O12" s="30" t="n"/>
-      <c r="P12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" s="70">
-      <c r="A13" s="54" t="inlineStr">
+      <c r="K12" s="93" t="n"/>
+      <c r="L12" s="89" t="n"/>
+      <c r="M12" s="68" t="n"/>
+      <c r="N12" s="93" t="n"/>
+      <c r="O12" s="93" t="n"/>
+      <c r="P12" s="89" t="n"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="127">
+      <c r="A13" s="137" t="inlineStr">
         <is>
           <t>1. DATOS BASE DEL AÑO (se llenan cada mes)</t>
         </is>
       </c>
-      <c r="B13" s="38" t="n"/>
-      <c r="C13" s="38" t="n"/>
-      <c r="D13" s="38" t="n"/>
-      <c r="E13" s="38" t="n"/>
-      <c r="F13" s="38" t="n"/>
-      <c r="G13" s="38" t="n"/>
-      <c r="H13" s="38" t="n"/>
-      <c r="I13" s="38" t="n"/>
-      <c r="J13" s="38" t="n"/>
-      <c r="K13" s="38" t="n"/>
-      <c r="L13" s="38" t="n"/>
-      <c r="M13" s="38" t="n"/>
-      <c r="N13" s="38" t="n"/>
-      <c r="O13" s="38" t="n"/>
-      <c r="P13" s="47" t="n"/>
-    </row>
-    <row r="14" ht="19" customHeight="1" s="70">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="B13" s="98" t="n"/>
+      <c r="C13" s="98" t="n"/>
+      <c r="D13" s="98" t="n"/>
+      <c r="E13" s="98" t="n"/>
+      <c r="F13" s="98" t="n"/>
+      <c r="G13" s="98" t="n"/>
+      <c r="H13" s="98" t="n"/>
+      <c r="I13" s="98" t="n"/>
+      <c r="J13" s="98" t="n"/>
+      <c r="K13" s="98" t="n"/>
+      <c r="L13" s="98" t="n"/>
+      <c r="M13" s="98" t="n"/>
+      <c r="N13" s="98" t="n"/>
+      <c r="O13" s="98" t="n"/>
+      <c r="P13" s="97" t="n"/>
+    </row>
+    <row r="14" ht="19.05" customHeight="1" s="127">
+      <c r="A14" s="74" t="inlineStr">
         <is>
           <t>Dato</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="74" t="inlineStr">
         <is>
           <t>Ene</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="74" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="74" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="74" t="inlineStr">
         <is>
           <t>Abr</t>
         </is>
       </c>
-      <c r="F14" s="34" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="G14" s="74" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr">
+      <c r="H14" s="74" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I14" s="34" t="inlineStr">
+      <c r="I14" s="74" t="inlineStr">
         <is>
           <t>Ago</t>
         </is>
       </c>
-      <c r="J14" s="34" t="inlineStr">
+      <c r="J14" s="74" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K14" s="34" t="inlineStr">
+      <c r="K14" s="74" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L14" s="34" t="inlineStr">
+      <c r="L14" s="74" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M14" s="34" t="inlineStr">
+      <c r="M14" s="74" t="inlineStr">
         <is>
           <t>Dic</t>
         </is>
       </c>
-      <c r="N14" s="34" t="inlineStr">
+      <c r="N14" s="74" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="O14" s="34" t="inlineStr">
+      <c r="O14" s="74" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="P14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1" s="70">
-      <c r="A15" s="117" t="inlineStr">
+      <c r="P14" s="89" t="n"/>
+    </row>
+    <row r="15" ht="16.95" customHeight="1" s="127">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Promedio de trabajadores</t>
         </is>
       </c>
-      <c r="B15" s="57" t="n"/>
-      <c r="C15" s="57" t="n"/>
-      <c r="D15" s="57" t="n"/>
-      <c r="E15" s="57" t="n"/>
-      <c r="F15" s="57" t="n"/>
-      <c r="G15" s="57" t="n"/>
-      <c r="H15" s="57" t="n"/>
-      <c r="I15" s="57" t="n"/>
-      <c r="J15" s="57" t="n"/>
-      <c r="K15" s="57" t="n"/>
-      <c r="L15" s="57" t="n"/>
-      <c r="M15" s="57" t="n"/>
-      <c r="N15" s="118">
+      <c r="B15" s="126" t="n"/>
+      <c r="C15" s="126" t="n"/>
+      <c r="D15" s="126" t="n"/>
+      <c r="E15" s="126" t="n"/>
+      <c r="F15" s="126" t="n"/>
+      <c r="G15" s="126" t="n"/>
+      <c r="H15" s="126" t="n"/>
+      <c r="I15" s="126" t="n"/>
+      <c r="J15" s="126" t="n"/>
+      <c r="K15" s="126" t="n"/>
+      <c r="L15" s="126" t="n"/>
+      <c r="M15" s="126" t="n"/>
+      <c r="N15" s="175">
         <f>IFERROR(AVERAGE(B15:M15),"")</f>
         <v/>
       </c>
-      <c r="O15" s="57" t="n"/>
-      <c r="P15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1" s="70">
-      <c r="A16" s="117" t="inlineStr">
+      <c r="O15" s="126" t="n"/>
+      <c r="P15" s="89" t="n"/>
+    </row>
+    <row r="16" ht="16.95" customHeight="1" s="127">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Horas-hombre trabajadas (HHT)</t>
         </is>
       </c>
-      <c r="B16" s="57" t="n"/>
-      <c r="C16" s="57" t="n"/>
-      <c r="D16" s="57" t="n"/>
-      <c r="E16" s="57" t="n"/>
-      <c r="F16" s="57" t="n"/>
-      <c r="G16" s="57" t="n"/>
-      <c r="H16" s="57" t="n"/>
-      <c r="I16" s="57" t="n"/>
-      <c r="J16" s="57" t="n"/>
-      <c r="K16" s="57" t="n"/>
-      <c r="L16" s="57" t="n"/>
-      <c r="M16" s="57" t="n"/>
-      <c r="N16" s="119">
+      <c r="B16" s="126" t="n"/>
+      <c r="C16" s="126" t="n"/>
+      <c r="D16" s="126" t="n"/>
+      <c r="E16" s="126" t="n"/>
+      <c r="F16" s="126" t="n"/>
+      <c r="G16" s="126" t="n"/>
+      <c r="H16" s="126" t="n"/>
+      <c r="I16" s="126" t="n"/>
+      <c r="J16" s="126" t="n"/>
+      <c r="K16" s="126" t="n"/>
+      <c r="L16" s="126" t="n"/>
+      <c r="M16" s="126" t="n"/>
+      <c r="N16" s="176">
         <f>IF(COUNT(B16:M16)=0,"",SUM(B16:M16))</f>
         <v/>
       </c>
-      <c r="O16" s="57" t="n"/>
-      <c r="P16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1" s="70">
-      <c r="A17" s="117" t="inlineStr">
+      <c r="O16" s="126" t="n"/>
+      <c r="P16" s="89" t="n"/>
+    </row>
+    <row r="17" ht="16.95" customHeight="1" s="127">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Accidentes de trabajo (AT)</t>
         </is>
       </c>
-      <c r="B17" s="57" t="n"/>
-      <c r="C17" s="57" t="n"/>
-      <c r="D17" s="57" t="n"/>
-      <c r="E17" s="57" t="n"/>
-      <c r="F17" s="57" t="n"/>
-      <c r="G17" s="57" t="n"/>
-      <c r="H17" s="57" t="n"/>
-      <c r="I17" s="57" t="n"/>
-      <c r="J17" s="57" t="n"/>
-      <c r="K17" s="57" t="n"/>
-      <c r="L17" s="57" t="n"/>
-      <c r="M17" s="57" t="n"/>
-      <c r="N17" s="119">
+      <c r="B17" s="126" t="n"/>
+      <c r="C17" s="126" t="n"/>
+      <c r="D17" s="126" t="n"/>
+      <c r="E17" s="126" t="n"/>
+      <c r="F17" s="126" t="n"/>
+      <c r="G17" s="126" t="n"/>
+      <c r="H17" s="126" t="n"/>
+      <c r="I17" s="126" t="n"/>
+      <c r="J17" s="126" t="n"/>
+      <c r="K17" s="126" t="n"/>
+      <c r="L17" s="126" t="n"/>
+      <c r="M17" s="126" t="n"/>
+      <c r="N17" s="176">
         <f>IF(COUNT(B17:M17)=0,"",SUM(B17:M17))</f>
         <v/>
       </c>
-      <c r="O17" s="57" t="n"/>
-      <c r="P17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1" s="70">
-      <c r="A18" s="117" t="inlineStr">
+      <c r="O17" s="126" t="n"/>
+      <c r="P17" s="89" t="n"/>
+    </row>
+    <row r="18" ht="16.95" customHeight="1" s="127">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>AT con incapacidad</t>
         </is>
       </c>
-      <c r="B18" s="57" t="n"/>
-      <c r="C18" s="57" t="n"/>
-      <c r="D18" s="57" t="n"/>
-      <c r="E18" s="57" t="n"/>
-      <c r="F18" s="57" t="n"/>
-      <c r="G18" s="57" t="n"/>
-      <c r="H18" s="57" t="n"/>
-      <c r="I18" s="57" t="n"/>
-      <c r="J18" s="57" t="n"/>
-      <c r="K18" s="57" t="n"/>
-      <c r="L18" s="57" t="n"/>
-      <c r="M18" s="57" t="n"/>
-      <c r="N18" s="119">
+      <c r="B18" s="126" t="n"/>
+      <c r="C18" s="126" t="n"/>
+      <c r="D18" s="126" t="n"/>
+      <c r="E18" s="126" t="n"/>
+      <c r="F18" s="126" t="n"/>
+      <c r="G18" s="126" t="n"/>
+      <c r="H18" s="126" t="n"/>
+      <c r="I18" s="126" t="n"/>
+      <c r="J18" s="126" t="n"/>
+      <c r="K18" s="126" t="n"/>
+      <c r="L18" s="126" t="n"/>
+      <c r="M18" s="126" t="n"/>
+      <c r="N18" s="176">
         <f>IF(COUNT(B18:M18)=0,"",SUM(B18:M18))</f>
         <v/>
       </c>
-      <c r="O18" s="57" t="n"/>
-      <c r="P18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="17" customHeight="1" s="70">
-      <c r="A19" s="117" t="inlineStr">
+      <c r="O18" s="126" t="n"/>
+      <c r="P18" s="89" t="n"/>
+    </row>
+    <row r="19" ht="16.95" customHeight="1" s="127">
+      <c r="A19" s="52" t="inlineStr">
         <is>
           <t>Días de incapacidad por AT</t>
         </is>
       </c>
-      <c r="B19" s="57" t="n"/>
-      <c r="C19" s="57" t="n"/>
-      <c r="D19" s="57" t="n"/>
-      <c r="E19" s="57" t="n"/>
-      <c r="F19" s="57" t="n"/>
-      <c r="G19" s="57" t="n"/>
-      <c r="H19" s="57" t="n"/>
-      <c r="I19" s="57" t="n"/>
-      <c r="J19" s="57" t="n"/>
-      <c r="K19" s="57" t="n"/>
-      <c r="L19" s="57" t="n"/>
-      <c r="M19" s="57" t="n"/>
-      <c r="N19" s="119">
+      <c r="B19" s="126" t="n"/>
+      <c r="C19" s="126" t="n"/>
+      <c r="D19" s="126" t="n"/>
+      <c r="E19" s="126" t="n"/>
+      <c r="F19" s="126" t="n"/>
+      <c r="G19" s="126" t="n"/>
+      <c r="H19" s="126" t="n"/>
+      <c r="I19" s="126" t="n"/>
+      <c r="J19" s="126" t="n"/>
+      <c r="K19" s="126" t="n"/>
+      <c r="L19" s="126" t="n"/>
+      <c r="M19" s="126" t="n"/>
+      <c r="N19" s="176">
         <f>IF(COUNT(B19:M19)=0,"",SUM(B19:M19))</f>
         <v/>
       </c>
-      <c r="O19" s="57" t="n"/>
-      <c r="P19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1" s="70">
-      <c r="A20" s="117" t="inlineStr">
+      <c r="O19" s="126" t="n"/>
+      <c r="P19" s="89" t="n"/>
+    </row>
+    <row r="20" ht="16.95" customHeight="1" s="127">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>AT mortales</t>
         </is>
       </c>
-      <c r="B20" s="57" t="n"/>
-      <c r="C20" s="57" t="n"/>
-      <c r="D20" s="57" t="n"/>
-      <c r="E20" s="57" t="n"/>
-      <c r="F20" s="57" t="n"/>
-      <c r="G20" s="57" t="n"/>
-      <c r="H20" s="57" t="n"/>
-      <c r="I20" s="57" t="n"/>
-      <c r="J20" s="57" t="n"/>
-      <c r="K20" s="57" t="n"/>
-      <c r="L20" s="57" t="n"/>
-      <c r="M20" s="57" t="n"/>
-      <c r="N20" s="119">
+      <c r="B20" s="126" t="n"/>
+      <c r="C20" s="126" t="n"/>
+      <c r="D20" s="126" t="n"/>
+      <c r="E20" s="126" t="n"/>
+      <c r="F20" s="126" t="n"/>
+      <c r="G20" s="126" t="n"/>
+      <c r="H20" s="126" t="n"/>
+      <c r="I20" s="126" t="n"/>
+      <c r="J20" s="126" t="n"/>
+      <c r="K20" s="126" t="n"/>
+      <c r="L20" s="126" t="n"/>
+      <c r="M20" s="126" t="n"/>
+      <c r="N20" s="176">
         <f>IF(COUNT(B20:M20)=0,"",SUM(B20:M20))</f>
         <v/>
       </c>
-      <c r="O20" s="57" t="n"/>
-      <c r="P20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1" s="70">
-      <c r="A21" s="117" t="inlineStr">
+      <c r="O20" s="126" t="n"/>
+      <c r="P20" s="89" t="n"/>
+    </row>
+    <row r="21" ht="16.95" customHeight="1" s="127">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>Casos nuevos de enfermedad laboral</t>
         </is>
       </c>
-      <c r="B21" s="57" t="n"/>
-      <c r="C21" s="57" t="n"/>
-      <c r="D21" s="57" t="n"/>
-      <c r="E21" s="57" t="n"/>
-      <c r="F21" s="57" t="n"/>
-      <c r="G21" s="57" t="n"/>
-      <c r="H21" s="57" t="n"/>
-      <c r="I21" s="57" t="n"/>
-      <c r="J21" s="57" t="n"/>
-      <c r="K21" s="57" t="n"/>
-      <c r="L21" s="57" t="n"/>
-      <c r="M21" s="57" t="n"/>
-      <c r="N21" s="119">
+      <c r="B21" s="126" t="n"/>
+      <c r="C21" s="126" t="n"/>
+      <c r="D21" s="126" t="n"/>
+      <c r="E21" s="126" t="n"/>
+      <c r="F21" s="126" t="n"/>
+      <c r="G21" s="126" t="n"/>
+      <c r="H21" s="126" t="n"/>
+      <c r="I21" s="126" t="n"/>
+      <c r="J21" s="126" t="n"/>
+      <c r="K21" s="126" t="n"/>
+      <c r="L21" s="126" t="n"/>
+      <c r="M21" s="126" t="n"/>
+      <c r="N21" s="176">
         <f>IF(COUNT(B21:M21)=0,"",SUM(B21:M21))</f>
         <v/>
       </c>
-      <c r="O21" s="57" t="n"/>
-      <c r="P21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1" s="70">
-      <c r="A22" s="117" t="inlineStr">
+      <c r="O21" s="126" t="n"/>
+      <c r="P21" s="89" t="n"/>
+    </row>
+    <row r="22" ht="16.95" customHeight="1" s="127">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>Casos antiguos de enfermedad laboral</t>
         </is>
       </c>
-      <c r="B22" s="57" t="n"/>
-      <c r="C22" s="57" t="n"/>
-      <c r="D22" s="57" t="n"/>
-      <c r="E22" s="57" t="n"/>
-      <c r="F22" s="57" t="n"/>
-      <c r="G22" s="57" t="n"/>
-      <c r="H22" s="57" t="n"/>
-      <c r="I22" s="57" t="n"/>
-      <c r="J22" s="57" t="n"/>
-      <c r="K22" s="57" t="n"/>
-      <c r="L22" s="57" t="n"/>
-      <c r="M22" s="57" t="n"/>
-      <c r="N22" s="119">
+      <c r="B22" s="126" t="n"/>
+      <c r="C22" s="126" t="n"/>
+      <c r="D22" s="126" t="n"/>
+      <c r="E22" s="126" t="n"/>
+      <c r="F22" s="126" t="n"/>
+      <c r="G22" s="126" t="n"/>
+      <c r="H22" s="126" t="n"/>
+      <c r="I22" s="126" t="n"/>
+      <c r="J22" s="126" t="n"/>
+      <c r="K22" s="126" t="n"/>
+      <c r="L22" s="126" t="n"/>
+      <c r="M22" s="126" t="n"/>
+      <c r="N22" s="176">
         <f>IF(COUNT(B22:M22)=0,"",SUM(B22:M22))</f>
         <v/>
       </c>
-      <c r="O22" s="57" t="n"/>
-      <c r="P22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="17" customHeight="1" s="70">
-      <c r="A23" s="117" t="inlineStr">
+      <c r="O22" s="126" t="n"/>
+      <c r="P22" s="89" t="n"/>
+    </row>
+    <row r="23" ht="16.95" customHeight="1" s="127">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>Incidentes y casi accidentes</t>
         </is>
       </c>
-      <c r="B23" s="57" t="n"/>
-      <c r="C23" s="57" t="n"/>
-      <c r="D23" s="57" t="n"/>
-      <c r="E23" s="57" t="n"/>
-      <c r="F23" s="57" t="n"/>
-      <c r="G23" s="57" t="n"/>
-      <c r="H23" s="57" t="n"/>
-      <c r="I23" s="57" t="n"/>
-      <c r="J23" s="57" t="n"/>
-      <c r="K23" s="57" t="n"/>
-      <c r="L23" s="57" t="n"/>
-      <c r="M23" s="57" t="n"/>
-      <c r="N23" s="119">
+      <c r="B23" s="126" t="n"/>
+      <c r="C23" s="126" t="n"/>
+      <c r="D23" s="126" t="n"/>
+      <c r="E23" s="126" t="n"/>
+      <c r="F23" s="126" t="n"/>
+      <c r="G23" s="126" t="n"/>
+      <c r="H23" s="126" t="n"/>
+      <c r="I23" s="126" t="n"/>
+      <c r="J23" s="126" t="n"/>
+      <c r="K23" s="126" t="n"/>
+      <c r="L23" s="126" t="n"/>
+      <c r="M23" s="126" t="n"/>
+      <c r="N23" s="176">
         <f>IF(COUNT(B23:M23)=0,"",SUM(B23:M23))</f>
         <v/>
       </c>
-      <c r="O23" s="57" t="n"/>
-      <c r="P23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1" s="70">
-      <c r="A24" s="117" t="inlineStr">
+      <c r="O23" s="126" t="n"/>
+      <c r="P23" s="89" t="n"/>
+    </row>
+    <row r="24" ht="16.95" customHeight="1" s="127">
+      <c r="A24" s="52" t="inlineStr">
         <is>
           <t>Días de ausencia por incapacidad médica</t>
         </is>
       </c>
-      <c r="B24" s="57" t="n"/>
-      <c r="C24" s="57" t="n"/>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="57" t="n"/>
-      <c r="G24" s="57" t="n"/>
-      <c r="H24" s="57" t="n"/>
-      <c r="I24" s="57" t="n"/>
-      <c r="J24" s="57" t="n"/>
-      <c r="K24" s="57" t="n"/>
-      <c r="L24" s="57" t="n"/>
-      <c r="M24" s="57" t="n"/>
-      <c r="N24" s="119">
+      <c r="B24" s="126" t="n"/>
+      <c r="C24" s="126" t="n"/>
+      <c r="D24" s="126" t="n"/>
+      <c r="E24" s="126" t="n"/>
+      <c r="F24" s="126" t="n"/>
+      <c r="G24" s="126" t="n"/>
+      <c r="H24" s="126" t="n"/>
+      <c r="I24" s="126" t="n"/>
+      <c r="J24" s="126" t="n"/>
+      <c r="K24" s="126" t="n"/>
+      <c r="L24" s="126" t="n"/>
+      <c r="M24" s="126" t="n"/>
+      <c r="N24" s="176">
         <f>IF(COUNT(B24:M24)=0,"",SUM(B24:M24))</f>
         <v/>
       </c>
-      <c r="O24" s="57" t="n"/>
-      <c r="P24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1" s="70">
-      <c r="A25" s="117" t="inlineStr">
+      <c r="O24" s="126" t="n"/>
+      <c r="P24" s="89" t="n"/>
+    </row>
+    <row r="25" ht="16.95" customHeight="1" s="127">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>Días de trabajo programados</t>
         </is>
       </c>
-      <c r="B25" s="57" t="n"/>
-      <c r="C25" s="57" t="n"/>
-      <c r="D25" s="57" t="n"/>
-      <c r="E25" s="57" t="n"/>
-      <c r="F25" s="57" t="n"/>
-      <c r="G25" s="57" t="n"/>
-      <c r="H25" s="57" t="n"/>
-      <c r="I25" s="57" t="n"/>
-      <c r="J25" s="57" t="n"/>
-      <c r="K25" s="57" t="n"/>
-      <c r="L25" s="57" t="n"/>
-      <c r="M25" s="57" t="n"/>
-      <c r="N25" s="119">
+      <c r="B25" s="126" t="n"/>
+      <c r="C25" s="126" t="n"/>
+      <c r="D25" s="126" t="n"/>
+      <c r="E25" s="126" t="n"/>
+      <c r="F25" s="126" t="n"/>
+      <c r="G25" s="126" t="n"/>
+      <c r="H25" s="126" t="n"/>
+      <c r="I25" s="126" t="n"/>
+      <c r="J25" s="126" t="n"/>
+      <c r="K25" s="126" t="n"/>
+      <c r="L25" s="126" t="n"/>
+      <c r="M25" s="126" t="n"/>
+      <c r="N25" s="176">
         <f>IF(COUNT(B25:M25)=0,"",SUM(B25:M25))</f>
         <v/>
       </c>
-      <c r="O25" s="57" t="n"/>
-      <c r="P25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" s="70">
-      <c r="A26" s="54" t="inlineStr">
+      <c r="O25" s="126" t="n"/>
+      <c r="P25" s="89" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="127">
+      <c r="A26" s="137" t="inlineStr">
         <is>
           <t>2. INDICADORES DE ACCIDENTALIDAD Y SALUD (se calculan solos)</t>
         </is>
       </c>
-      <c r="B26" s="38" t="n"/>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="38" t="n"/>
-      <c r="E26" s="38" t="n"/>
-      <c r="F26" s="38" t="n"/>
-      <c r="G26" s="38" t="n"/>
-      <c r="H26" s="38" t="n"/>
-      <c r="I26" s="38" t="n"/>
-      <c r="J26" s="38" t="n"/>
-      <c r="K26" s="38" t="n"/>
-      <c r="L26" s="38" t="n"/>
-      <c r="M26" s="38" t="n"/>
-      <c r="N26" s="38" t="n"/>
-      <c r="O26" s="38" t="n"/>
-      <c r="P26" s="47" t="n"/>
-    </row>
-    <row r="27" ht="19" customHeight="1" s="70">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="B26" s="98" t="n"/>
+      <c r="C26" s="98" t="n"/>
+      <c r="D26" s="98" t="n"/>
+      <c r="E26" s="98" t="n"/>
+      <c r="F26" s="98" t="n"/>
+      <c r="G26" s="98" t="n"/>
+      <c r="H26" s="98" t="n"/>
+      <c r="I26" s="98" t="n"/>
+      <c r="J26" s="98" t="n"/>
+      <c r="K26" s="98" t="n"/>
+      <c r="L26" s="98" t="n"/>
+      <c r="M26" s="98" t="n"/>
+      <c r="N26" s="98" t="n"/>
+      <c r="O26" s="98" t="n"/>
+      <c r="P26" s="97" t="n"/>
+    </row>
+    <row r="27" ht="19.05" customHeight="1" s="127">
+      <c r="A27" s="74" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B27" s="74" t="inlineStr">
         <is>
           <t>Ene</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C27" s="74" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D27" s="74" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E27" s="34" t="inlineStr">
+      <c r="E27" s="74" t="inlineStr">
         <is>
           <t>Abr</t>
         </is>
       </c>
-      <c r="F27" s="34" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
+      <c r="G27" s="74" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H27" s="34" t="inlineStr">
+      <c r="H27" s="74" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I27" s="34" t="inlineStr">
+      <c r="I27" s="74" t="inlineStr">
         <is>
           <t>Ago</t>
         </is>
       </c>
-      <c r="J27" s="34" t="inlineStr">
+      <c r="J27" s="74" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K27" s="34" t="inlineStr">
+      <c r="K27" s="74" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L27" s="34" t="inlineStr">
+      <c r="L27" s="74" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M27" s="34" t="inlineStr">
+      <c r="M27" s="74" t="inlineStr">
         <is>
           <t>Dic</t>
         </is>
       </c>
-      <c r="N27" s="34" t="inlineStr">
+      <c r="N27" s="74" t="inlineStr">
         <is>
           <t>Año (acum.)</t>
         </is>
       </c>
-      <c r="O27" s="34" t="inlineStr">
+      <c r="O27" s="74" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="P27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1" s="70">
-      <c r="A28" s="117" t="inlineStr">
+      <c r="P27" s="89" t="n"/>
+    </row>
+    <row r="28" ht="16.95" customHeight="1" s="127">
+      <c r="A28" s="52" t="inlineStr">
         <is>
           <t>Frecuencia de accidentalidad (%)</t>
         </is>
       </c>
-      <c r="B28" s="120">
+      <c r="B28" s="53">
         <f>IFERROR(IF(OR(B15="",B15=0,B17=""),"",B17/B15*100),"")</f>
         <v/>
       </c>
-      <c r="C28" s="120">
+      <c r="C28" s="53">
         <f>IFERROR(IF(OR(C15="",C15=0,C17=""),"",C17/C15*100),"")</f>
         <v/>
       </c>
-      <c r="D28" s="120">
+      <c r="D28" s="53">
         <f>IFERROR(IF(OR(D15="",D15=0,D17=""),"",D17/D15*100),"")</f>
         <v/>
       </c>
-      <c r="E28" s="120">
+      <c r="E28" s="53">
         <f>IFERROR(IF(OR(E15="",E15=0,E17=""),"",E17/E15*100),"")</f>
         <v/>
       </c>
-      <c r="F28" s="120">
+      <c r="F28" s="53">
         <f>IFERROR(IF(OR(F15="",F15=0,F17=""),"",F17/F15*100),"")</f>
         <v/>
       </c>
-      <c r="G28" s="120">
+      <c r="G28" s="53">
         <f>IFERROR(IF(OR(G15="",G15=0,G17=""),"",G17/G15*100),"")</f>
         <v/>
       </c>
-      <c r="H28" s="120">
+      <c r="H28" s="53">
         <f>IFERROR(IF(OR(H15="",H15=0,H17=""),"",H17/H15*100),"")</f>
         <v/>
       </c>
-      <c r="I28" s="120">
+      <c r="I28" s="53">
         <f>IFERROR(IF(OR(I15="",I15=0,I17=""),"",I17/I15*100),"")</f>
         <v/>
       </c>
-      <c r="J28" s="120">
+      <c r="J28" s="53">
         <f>IFERROR(IF(OR(J15="",J15=0,J17=""),"",J17/J15*100),"")</f>
         <v/>
       </c>
-      <c r="K28" s="120">
+      <c r="K28" s="53">
         <f>IFERROR(IF(OR(K15="",K15=0,K17=""),"",K17/K15*100),"")</f>
         <v/>
       </c>
-      <c r="L28" s="120">
+      <c r="L28" s="53">
         <f>IFERROR(IF(OR(L15="",L15=0,L17=""),"",L17/L15*100),"")</f>
         <v/>
       </c>
-      <c r="M28" s="120">
+      <c r="M28" s="53">
         <f>IFERROR(IF(OR(M15="",M15=0,M17=""),"",M17/M15*100),"")</f>
         <v/>
       </c>
-      <c r="N28" s="120">
+      <c r="N28" s="53">
         <f>IFERROR(IF(OR(N15="",N15=0,N17=""),"",N17/N15*100),"")</f>
         <v/>
       </c>
-      <c r="O28" s="57" t="n"/>
-      <c r="P28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1" s="70">
-      <c r="A29" s="117" t="inlineStr">
+      <c r="O28" s="126" t="n"/>
+      <c r="P28" s="89" t="n"/>
+    </row>
+    <row r="29" ht="16.95" customHeight="1" s="127">
+      <c r="A29" s="52" t="inlineStr">
         <is>
           <t>Severidad de accidentalidad (%)</t>
         </is>
       </c>
-      <c r="B29" s="120">
+      <c r="B29" s="53">
         <f>IFERROR(IF(OR(B15="",B15=0,B19=""),"",B19/B15*100),"")</f>
         <v/>
       </c>
-      <c r="C29" s="120">
+      <c r="C29" s="53">
         <f>IFERROR(IF(OR(C15="",C15=0,C19=""),"",C19/C15*100),"")</f>
         <v/>
       </c>
-      <c r="D29" s="120">
+      <c r="D29" s="53">
         <f>IFERROR(IF(OR(D15="",D15=0,D19=""),"",D19/D15*100),"")</f>
         <v/>
       </c>
-      <c r="E29" s="120">
+      <c r="E29" s="53">
         <f>IFERROR(IF(OR(E15="",E15=0,E19=""),"",E19/E15*100),"")</f>
         <v/>
       </c>
-      <c r="F29" s="120">
+      <c r="F29" s="53">
         <f>IFERROR(IF(OR(F15="",F15=0,F19=""),"",F19/F15*100),"")</f>
         <v/>
       </c>
-      <c r="G29" s="120">
+      <c r="G29" s="53">
         <f>IFERROR(IF(OR(G15="",G15=0,G19=""),"",G19/G15*100),"")</f>
         <v/>
       </c>
-      <c r="H29" s="120">
+      <c r="H29" s="53">
         <f>IFERROR(IF(OR(H15="",H15=0,H19=""),"",H19/H15*100),"")</f>
         <v/>
       </c>
-      <c r="I29" s="120">
+      <c r="I29" s="53">
         <f>IFERROR(IF(OR(I15="",I15=0,I19=""),"",I19/I15*100),"")</f>
         <v/>
       </c>
-      <c r="J29" s="120">
+      <c r="J29" s="53">
         <f>IFERROR(IF(OR(J15="",J15=0,J19=""),"",J19/J15*100),"")</f>
         <v/>
       </c>
-      <c r="K29" s="120">
+      <c r="K29" s="53">
         <f>IFERROR(IF(OR(K15="",K15=0,K19=""),"",K19/K15*100),"")</f>
         <v/>
       </c>
-      <c r="L29" s="120">
+      <c r="L29" s="53">
         <f>IFERROR(IF(OR(L15="",L15=0,L19=""),"",L19/L15*100),"")</f>
         <v/>
       </c>
-      <c r="M29" s="120">
+      <c r="M29" s="53">
         <f>IFERROR(IF(OR(M15="",M15=0,M19=""),"",M19/M15*100),"")</f>
         <v/>
       </c>
-      <c r="N29" s="120">
+      <c r="N29" s="53">
         <f>IFERROR(IF(OR(N15="",N15=0,N19=""),"",N19/N15*100),"")</f>
         <v/>
       </c>
-      <c r="O29" s="57" t="n"/>
-      <c r="P29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1" s="70">
-      <c r="A30" s="117" t="inlineStr">
+      <c r="O29" s="126" t="n"/>
+      <c r="P29" s="89" t="n"/>
+    </row>
+    <row r="30" ht="16.95" customHeight="1" s="127">
+      <c r="A30" s="52" t="inlineStr">
         <is>
           <t>Proporción de AT mortales (%)</t>
         </is>
       </c>
-      <c r="B30" s="120">
+      <c r="B30" s="53">
         <f>IFERROR(IF(OR(B17="",B17=0,B20=""),"",B20/B17*100),"")</f>
         <v/>
       </c>
-      <c r="C30" s="120">
+      <c r="C30" s="53">
         <f>IFERROR(IF(OR(C17="",C17=0,C20=""),"",C20/C17*100),"")</f>
         <v/>
       </c>
-      <c r="D30" s="120">
+      <c r="D30" s="53">
         <f>IFERROR(IF(OR(D17="",D17=0,D20=""),"",D20/D17*100),"")</f>
         <v/>
       </c>
-      <c r="E30" s="120">
+      <c r="E30" s="53">
         <f>IFERROR(IF(OR(E17="",E17=0,E20=""),"",E20/E17*100),"")</f>
         <v/>
       </c>
-      <c r="F30" s="120">
+      <c r="F30" s="53">
         <f>IFERROR(IF(OR(F17="",F17=0,F20=""),"",F20/F17*100),"")</f>
         <v/>
       </c>
-      <c r="G30" s="120">
+      <c r="G30" s="53">
         <f>IFERROR(IF(OR(G17="",G17=0,G20=""),"",G20/G17*100),"")</f>
         <v/>
       </c>
-      <c r="H30" s="120">
+      <c r="H30" s="53">
         <f>IFERROR(IF(OR(H17="",H17=0,H20=""),"",H20/H17*100),"")</f>
         <v/>
       </c>
-      <c r="I30" s="120">
+      <c r="I30" s="53">
         <f>IFERROR(IF(OR(I17="",I17=0,I20=""),"",I20/I17*100),"")</f>
         <v/>
       </c>
-      <c r="J30" s="120">
+      <c r="J30" s="53">
         <f>IFERROR(IF(OR(J17="",J17=0,J20=""),"",J20/J17*100),"")</f>
         <v/>
       </c>
-      <c r="K30" s="120">
+      <c r="K30" s="53">
         <f>IFERROR(IF(OR(K17="",K17=0,K20=""),"",K20/K17*100),"")</f>
         <v/>
       </c>
-      <c r="L30" s="120">
+      <c r="L30" s="53">
         <f>IFERROR(IF(OR(L17="",L17=0,L20=""),"",L20/L17*100),"")</f>
         <v/>
       </c>
-      <c r="M30" s="120">
+      <c r="M30" s="53">
         <f>IFERROR(IF(OR(M17="",M17=0,M20=""),"",M20/M17*100),"")</f>
         <v/>
       </c>
-      <c r="N30" s="120">
+      <c r="N30" s="53">
         <f>IFERROR(IF(OR(N17="",N17=0,N20=""),"",N20/N17*100),"")</f>
         <v/>
       </c>
-      <c r="O30" s="57" t="n"/>
-      <c r="P30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1" s="70">
-      <c r="A31" s="117" t="inlineStr">
+      <c r="O30" s="126" t="n"/>
+      <c r="P30" s="89" t="n"/>
+    </row>
+    <row r="31" ht="16.95" customHeight="1" s="127">
+      <c r="A31" s="52" t="inlineStr">
         <is>
           <t>Incidencia de enfermedad laboral (por 100.000)</t>
         </is>
       </c>
-      <c r="B31" s="120">
+      <c r="B31" s="53">
         <f>IFERROR(IF(OR(B15="",B15=0,B21=""),"",B21/B15*100000),"")</f>
         <v/>
       </c>
-      <c r="C31" s="120">
+      <c r="C31" s="53">
         <f>IFERROR(IF(OR(C15="",C15=0,C21=""),"",C21/C15*100000),"")</f>
         <v/>
       </c>
-      <c r="D31" s="120">
+      <c r="D31" s="53">
         <f>IFERROR(IF(OR(D15="",D15=0,D21=""),"",D21/D15*100000),"")</f>
         <v/>
       </c>
-      <c r="E31" s="120">
+      <c r="E31" s="53">
         <f>IFERROR(IF(OR(E15="",E15=0,E21=""),"",E21/E15*100000),"")</f>
         <v/>
       </c>
-      <c r="F31" s="120">
+      <c r="F31" s="53">
         <f>IFERROR(IF(OR(F15="",F15=0,F21=""),"",F21/F15*100000),"")</f>
         <v/>
       </c>
-      <c r="G31" s="120">
+      <c r="G31" s="53">
         <f>IFERROR(IF(OR(G15="",G15=0,G21=""),"",G21/G15*100000),"")</f>
         <v/>
       </c>
-      <c r="H31" s="120">
+      <c r="H31" s="53">
         <f>IFERROR(IF(OR(H15="",H15=0,H21=""),"",H21/H15*100000),"")</f>
         <v/>
       </c>
-      <c r="I31" s="120">
+      <c r="I31" s="53">
         <f>IFERROR(IF(OR(I15="",I15=0,I21=""),"",I21/I15*100000),"")</f>
         <v/>
       </c>
-      <c r="J31" s="120">
+      <c r="J31" s="53">
         <f>IFERROR(IF(OR(J15="",J15=0,J21=""),"",J21/J15*100000),"")</f>
         <v/>
       </c>
-      <c r="K31" s="120">
+      <c r="K31" s="53">
         <f>IFERROR(IF(OR(K15="",K15=0,K21=""),"",K21/K15*100000),"")</f>
         <v/>
       </c>
-      <c r="L31" s="120">
+      <c r="L31" s="53">
         <f>IFERROR(IF(OR(L15="",L15=0,L21=""),"",L21/L15*100000),"")</f>
         <v/>
       </c>
-      <c r="M31" s="120">
+      <c r="M31" s="53">
         <f>IFERROR(IF(OR(M15="",M15=0,M21=""),"",M21/M15*100000),"")</f>
         <v/>
       </c>
-      <c r="N31" s="120">
+      <c r="N31" s="53">
         <f>IFERROR(IF(OR(N15="",N15=0,N21=""),"",N21/N15*100000),"")</f>
         <v/>
       </c>
-      <c r="O31" s="57" t="n"/>
-      <c r="P31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="17" customHeight="1" s="70">
-      <c r="A32" s="117" t="inlineStr">
+      <c r="O31" s="126" t="n"/>
+      <c r="P31" s="89" t="n"/>
+    </row>
+    <row r="32" ht="16.95" customHeight="1" s="127">
+      <c r="A32" s="52" t="inlineStr">
         <is>
           <t>Prevalencia de enfermedad laboral (por 100.000)</t>
         </is>
       </c>
-      <c r="B32" s="120">
+      <c r="B32" s="53">
         <f>IFERROR(IF(OR(B15="",B15=0,AND(B21="",B22="")),"",(B21+B22)/B15*100000),"")</f>
         <v/>
       </c>
-      <c r="C32" s="120">
+      <c r="C32" s="53">
         <f>IFERROR(IF(OR(C15="",C15=0,AND(C21="",C22="")),"",(C21+C22)/C15*100000),"")</f>
         <v/>
       </c>
-      <c r="D32" s="120">
+      <c r="D32" s="53">
         <f>IFERROR(IF(OR(D15="",D15=0,AND(D21="",D22="")),"",(D21+D22)/D15*100000),"")</f>
         <v/>
       </c>
-      <c r="E32" s="120">
+      <c r="E32" s="53">
         <f>IFERROR(IF(OR(E15="",E15=0,AND(E21="",E22="")),"",(E21+E22)/E15*100000),"")</f>
         <v/>
       </c>
-      <c r="F32" s="120">
+      <c r="F32" s="53">
         <f>IFERROR(IF(OR(F15="",F15=0,AND(F21="",F22="")),"",(F21+F22)/F15*100000),"")</f>
         <v/>
       </c>
-      <c r="G32" s="120">
+      <c r="G32" s="53">
         <f>IFERROR(IF(OR(G15="",G15=0,AND(G21="",G22="")),"",(G21+G22)/G15*100000),"")</f>
         <v/>
       </c>
-      <c r="H32" s="120">
+      <c r="H32" s="53">
         <f>IFERROR(IF(OR(H15="",H15=0,AND(H21="",H22="")),"",(H21+H22)/H15*100000),"")</f>
         <v/>
       </c>
-      <c r="I32" s="120">
+      <c r="I32" s="53">
         <f>IFERROR(IF(OR(I15="",I15=0,AND(I21="",I22="")),"",(I21+I22)/I15*100000),"")</f>
         <v/>
       </c>
-      <c r="J32" s="120">
+      <c r="J32" s="53">
         <f>IFERROR(IF(OR(J15="",J15=0,AND(J21="",J22="")),"",(J21+J22)/J15*100000),"")</f>
         <v/>
       </c>
-      <c r="K32" s="120">
+      <c r="K32" s="53">
         <f>IFERROR(IF(OR(K15="",K15=0,AND(K21="",K22="")),"",(K21+K22)/K15*100000),"")</f>
         <v/>
       </c>
-      <c r="L32" s="120">
+      <c r="L32" s="53">
         <f>IFERROR(IF(OR(L15="",L15=0,AND(L21="",L22="")),"",(L21+L22)/L15*100000),"")</f>
         <v/>
       </c>
-      <c r="M32" s="120">
+      <c r="M32" s="53">
         <f>IFERROR(IF(OR(M15="",M15=0,AND(M21="",M22="")),"",(M21+M22)/M15*100000),"")</f>
         <v/>
       </c>
-      <c r="N32" s="120">
+      <c r="N32" s="53">
         <f>IFERROR(IF(OR(N15="",N15=0,AND(N21="",N22="")),"",(N21+N22)/N15*100000),"")</f>
         <v/>
       </c>
-      <c r="O32" s="57" t="n"/>
-      <c r="P32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="17" customHeight="1" s="70">
-      <c r="A33" s="117" t="inlineStr">
+      <c r="O32" s="126" t="n"/>
+      <c r="P32" s="89" t="n"/>
+    </row>
+    <row r="33" ht="16.95" customHeight="1" s="127">
+      <c r="A33" s="52" t="inlineStr">
         <is>
           <t>Ausentismo por causa médica (%)</t>
         </is>
       </c>
-      <c r="B33" s="120">
+      <c r="B33" s="53">
         <f>IFERROR(IF(OR(B25="",B25=0,B24=""),"",B24/B25*100),"")</f>
         <v/>
       </c>
-      <c r="C33" s="120">
+      <c r="C33" s="53">
         <f>IFERROR(IF(OR(C25="",C25=0,C24=""),"",C24/C25*100),"")</f>
         <v/>
       </c>
-      <c r="D33" s="120">
+      <c r="D33" s="53">
         <f>IFERROR(IF(OR(D25="",D25=0,D24=""),"",D24/D25*100),"")</f>
         <v/>
       </c>
-      <c r="E33" s="120">
+      <c r="E33" s="53">
         <f>IFERROR(IF(OR(E25="",E25=0,E24=""),"",E24/E25*100),"")</f>
         <v/>
       </c>
-      <c r="F33" s="120">
+      <c r="F33" s="53">
         <f>IFERROR(IF(OR(F25="",F25=0,F24=""),"",F24/F25*100),"")</f>
         <v/>
       </c>
-      <c r="G33" s="120">
+      <c r="G33" s="53">
         <f>IFERROR(IF(OR(G25="",G25=0,G24=""),"",G24/G25*100),"")</f>
         <v/>
       </c>
-      <c r="H33" s="120">
+      <c r="H33" s="53">
         <f>IFERROR(IF(OR(H25="",H25=0,H24=""),"",H24/H25*100),"")</f>
         <v/>
       </c>
-      <c r="I33" s="120">
+      <c r="I33" s="53">
         <f>IFERROR(IF(OR(I25="",I25=0,I24=""),"",I24/I25*100),"")</f>
         <v/>
       </c>
-      <c r="J33" s="120">
+      <c r="J33" s="53">
         <f>IFERROR(IF(OR(J25="",J25=0,J24=""),"",J24/J25*100),"")</f>
         <v/>
       </c>
-      <c r="K33" s="120">
+      <c r="K33" s="53">
         <f>IFERROR(IF(OR(K25="",K25=0,K24=""),"",K24/K25*100),"")</f>
         <v/>
       </c>
-      <c r="L33" s="120">
+      <c r="L33" s="53">
         <f>IFERROR(IF(OR(L25="",L25=0,L24=""),"",L24/L25*100),"")</f>
         <v/>
       </c>
-      <c r="M33" s="120">
+      <c r="M33" s="53">
         <f>IFERROR(IF(OR(M25="",M25=0,M24=""),"",M24/M25*100),"")</f>
         <v/>
       </c>
-      <c r="N33" s="120">
+      <c r="N33" s="53">
         <f>IFERROR(IF(OR(N25="",N25=0,N24=""),"",N24/N25*100),"")</f>
         <v/>
       </c>
-      <c r="O33" s="57" t="n"/>
-      <c r="P33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="17" customHeight="1" s="70">
-      <c r="A34" s="117" t="inlineStr">
+      <c r="O33" s="126" t="n"/>
+      <c r="P33" s="89" t="n"/>
+    </row>
+    <row r="34" ht="16.95" customHeight="1" s="127">
+      <c r="A34" s="52" t="inlineStr">
         <is>
           <t>Índice de frecuencia, IF (AT × 240.000 ÷ HHT)</t>
         </is>
       </c>
-      <c r="B34" s="120">
+      <c r="B34" s="53">
         <f>IFERROR(IF(OR(B16="",B16=0,B17=""),"",B17*240000/B16),"")</f>
         <v/>
       </c>
-      <c r="C34" s="120">
+      <c r="C34" s="53">
         <f>IFERROR(IF(OR(C16="",C16=0,C17=""),"",C17*240000/C16),"")</f>
         <v/>
       </c>
-      <c r="D34" s="120">
+      <c r="D34" s="53">
         <f>IFERROR(IF(OR(D16="",D16=0,D17=""),"",D17*240000/D16),"")</f>
         <v/>
       </c>
-      <c r="E34" s="120">
+      <c r="E34" s="53">
         <f>IFERROR(IF(OR(E16="",E16=0,E17=""),"",E17*240000/E16),"")</f>
         <v/>
       </c>
-      <c r="F34" s="120">
+      <c r="F34" s="53">
         <f>IFERROR(IF(OR(F16="",F16=0,F17=""),"",F17*240000/F16),"")</f>
         <v/>
       </c>
-      <c r="G34" s="120">
+      <c r="G34" s="53">
         <f>IFERROR(IF(OR(G16="",G16=0,G17=""),"",G17*240000/G16),"")</f>
         <v/>
       </c>
-      <c r="H34" s="120">
+      <c r="H34" s="53">
         <f>IFERROR(IF(OR(H16="",H16=0,H17=""),"",H17*240000/H16),"")</f>
         <v/>
       </c>
-      <c r="I34" s="120">
+      <c r="I34" s="53">
         <f>IFERROR(IF(OR(I16="",I16=0,I17=""),"",I17*240000/I16),"")</f>
         <v/>
       </c>
-      <c r="J34" s="120">
+      <c r="J34" s="53">
         <f>IFERROR(IF(OR(J16="",J16=0,J17=""),"",J17*240000/J16),"")</f>
         <v/>
       </c>
-      <c r="K34" s="120">
+      <c r="K34" s="53">
         <f>IFERROR(IF(OR(K16="",K16=0,K17=""),"",K17*240000/K16),"")</f>
         <v/>
       </c>
-      <c r="L34" s="120">
+      <c r="L34" s="53">
         <f>IFERROR(IF(OR(L16="",L16=0,L17=""),"",L17*240000/L16),"")</f>
         <v/>
       </c>
-      <c r="M34" s="120">
+      <c r="M34" s="53">
         <f>IFERROR(IF(OR(M16="",M16=0,M17=""),"",M17*240000/M16),"")</f>
         <v/>
       </c>
-      <c r="N34" s="120">
+      <c r="N34" s="53">
         <f>IFERROR(IF(OR(N16="",N16=0,N17=""),"",N17*240000/N16),"")</f>
         <v/>
       </c>
-      <c r="O34" s="57" t="n"/>
-      <c r="P34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="17" customHeight="1" s="70">
-      <c r="A35" s="117" t="inlineStr">
+      <c r="O34" s="126" t="n"/>
+      <c r="P34" s="89" t="n"/>
+    </row>
+    <row r="35" ht="16.95" customHeight="1" s="127">
+      <c r="A35" s="52" t="inlineStr">
         <is>
           <t>Índice de severidad, IS (días × 240.000 ÷ HHT)</t>
         </is>
       </c>
-      <c r="B35" s="120">
+      <c r="B35" s="53">
         <f>IFERROR(IF(OR(B16="",B16=0,B19=""),"",B19*240000/B16),"")</f>
         <v/>
       </c>
-      <c r="C35" s="120">
+      <c r="C35" s="53">
         <f>IFERROR(IF(OR(C16="",C16=0,C19=""),"",C19*240000/C16),"")</f>
         <v/>
       </c>
-      <c r="D35" s="120">
+      <c r="D35" s="53">
         <f>IFERROR(IF(OR(D16="",D16=0,D19=""),"",D19*240000/D16),"")</f>
         <v/>
       </c>
-      <c r="E35" s="120">
+      <c r="E35" s="53">
         <f>IFERROR(IF(OR(E16="",E16=0,E19=""),"",E19*240000/E16),"")</f>
         <v/>
       </c>
-      <c r="F35" s="120">
+      <c r="F35" s="53">
         <f>IFERROR(IF(OR(F16="",F16=0,F19=""),"",F19*240000/F16),"")</f>
         <v/>
       </c>
-      <c r="G35" s="120">
+      <c r="G35" s="53">
         <f>IFERROR(IF(OR(G16="",G16=0,G19=""),"",G19*240000/G16),"")</f>
         <v/>
       </c>
-      <c r="H35" s="120">
+      <c r="H35" s="53">
         <f>IFERROR(IF(OR(H16="",H16=0,H19=""),"",H19*240000/H16),"")</f>
         <v/>
       </c>
-      <c r="I35" s="120">
+      <c r="I35" s="53">
         <f>IFERROR(IF(OR(I16="",I16=0,I19=""),"",I19*240000/I16),"")</f>
         <v/>
       </c>
-      <c r="J35" s="120">
+      <c r="J35" s="53">
         <f>IFERROR(IF(OR(J16="",J16=0,J19=""),"",J19*240000/J16),"")</f>
         <v/>
       </c>
-      <c r="K35" s="120">
+      <c r="K35" s="53">
         <f>IFERROR(IF(OR(K16="",K16=0,K19=""),"",K19*240000/K16),"")</f>
         <v/>
       </c>
-      <c r="L35" s="120">
+      <c r="L35" s="53">
         <f>IFERROR(IF(OR(L16="",L16=0,L19=""),"",L19*240000/L16),"")</f>
         <v/>
       </c>
-      <c r="M35" s="120">
+      <c r="M35" s="53">
         <f>IFERROR(IF(OR(M16="",M16=0,M19=""),"",M19*240000/M16),"")</f>
         <v/>
       </c>
-      <c r="N35" s="120">
+      <c r="N35" s="53">
         <f>IFERROR(IF(OR(N16="",N16=0,N19=""),"",N19*240000/N16),"")</f>
         <v/>
       </c>
-      <c r="O35" s="57" t="n"/>
-      <c r="P35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1" s="70">
-      <c r="A36" s="117" t="inlineStr">
+      <c r="O35" s="126" t="n"/>
+      <c r="P35" s="89" t="n"/>
+    </row>
+    <row r="36" ht="16.95" customHeight="1" s="127">
+      <c r="A36" s="331" t="inlineStr">
         <is>
           <t>Índice de lesiones incapacitantes, ILI (IF × IS ÷ 1.000)</t>
         </is>
       </c>
-      <c r="B36" s="120">
+      <c r="B36" s="332">
         <f>IFERROR(IF(OR(B34="",B35=""),"",B34*B35/1000),"")</f>
         <v/>
       </c>
-      <c r="C36" s="120">
+      <c r="C36" s="332">
         <f>IFERROR(IF(OR(C34="",C35=""),"",C34*C35/1000),"")</f>
         <v/>
       </c>
-      <c r="D36" s="120">
+      <c r="D36" s="332">
         <f>IFERROR(IF(OR(D34="",D35=""),"",D34*D35/1000),"")</f>
         <v/>
       </c>
-      <c r="E36" s="120">
+      <c r="E36" s="332">
         <f>IFERROR(IF(OR(E34="",E35=""),"",E34*E35/1000),"")</f>
         <v/>
       </c>
-      <c r="F36" s="120">
+      <c r="F36" s="332">
         <f>IFERROR(IF(OR(F34="",F35=""),"",F34*F35/1000),"")</f>
         <v/>
       </c>
-      <c r="G36" s="120">
+      <c r="G36" s="332">
         <f>IFERROR(IF(OR(G34="",G35=""),"",G34*G35/1000),"")</f>
         <v/>
       </c>
-      <c r="H36" s="120">
+      <c r="H36" s="332">
         <f>IFERROR(IF(OR(H34="",H35=""),"",H34*H35/1000),"")</f>
         <v/>
       </c>
-      <c r="I36" s="120">
+      <c r="I36" s="332">
         <f>IFERROR(IF(OR(I34="",I35=""),"",I34*I35/1000),"")</f>
         <v/>
       </c>
-      <c r="J36" s="120">
+      <c r="J36" s="332">
         <f>IFERROR(IF(OR(J34="",J35=""),"",J34*J35/1000),"")</f>
         <v/>
       </c>
-      <c r="K36" s="120">
+      <c r="K36" s="332">
         <f>IFERROR(IF(OR(K34="",K35=""),"",K34*K35/1000),"")</f>
         <v/>
       </c>
-      <c r="L36" s="120">
+      <c r="L36" s="332">
         <f>IFERROR(IF(OR(L34="",L35=""),"",L34*L35/1000),"")</f>
         <v/>
       </c>
-      <c r="M36" s="120">
+      <c r="M36" s="332">
         <f>IFERROR(IF(OR(M34="",M35=""),"",M34*M35/1000),"")</f>
         <v/>
       </c>
-      <c r="N36" s="120">
+      <c r="N36" s="332">
         <f>IFERROR(IF(OR(N34="",N35=""),"",N34*N35/1000),"")</f>
         <v/>
       </c>
-      <c r="O36" s="57" t="n"/>
-      <c r="P36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="16" customHeight="1" s="70">
-      <c r="A37" s="103" t="inlineStr">
+      <c r="O36" s="337" t="n"/>
+      <c r="P36" s="94" t="n"/>
+    </row>
+    <row r="37" ht="16.05" customHeight="1" s="127">
+      <c r="A37" s="255" t="inlineStr">
         <is>
           <t>El año (acum.) se calcula con los totales del año (y el promedio de trabajadores). Meta: la define el proyecto. IF e IS usan K = 240.000 (100 trabajadores × 48 horas × 50 semanas).</t>
         </is>
       </c>
-      <c r="B37" s="115" t="n"/>
-      <c r="C37" s="115" t="n"/>
-      <c r="D37" s="115" t="n"/>
-      <c r="E37" s="115" t="n"/>
-      <c r="F37" s="115" t="n"/>
-      <c r="G37" s="115" t="n"/>
-      <c r="H37" s="115" t="n"/>
-      <c r="I37" s="115" t="n"/>
-      <c r="J37" s="115" t="n"/>
-      <c r="K37" s="115" t="n"/>
-      <c r="L37" s="115" t="n"/>
-      <c r="M37" s="115" t="n"/>
-      <c r="N37" s="115" t="n"/>
-      <c r="O37" s="115" t="n"/>
-      <c r="P37" s="116" t="n"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="70">
-      <c r="A38" s="54" t="inlineStr">
+      <c r="B37" s="349" t="n"/>
+      <c r="C37" s="349" t="n"/>
+      <c r="D37" s="349" t="n"/>
+      <c r="E37" s="349" t="n"/>
+      <c r="F37" s="349" t="n"/>
+      <c r="G37" s="349" t="n"/>
+      <c r="H37" s="349" t="n"/>
+      <c r="I37" s="349" t="n"/>
+      <c r="J37" s="349" t="n"/>
+      <c r="K37" s="349" t="n"/>
+      <c r="L37" s="349" t="n"/>
+      <c r="M37" s="349" t="n"/>
+      <c r="N37" s="349" t="n"/>
+      <c r="O37" s="349" t="n"/>
+      <c r="P37" s="351" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="127">
+      <c r="A38" s="137" t="inlineStr">
         <is>
           <t>3. INDICADORES DE GESTIÓN (programado vs. ejecutado)</t>
         </is>
       </c>
-      <c r="B38" s="38" t="n"/>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="38" t="n"/>
-      <c r="E38" s="38" t="n"/>
-      <c r="F38" s="38" t="n"/>
-      <c r="G38" s="38" t="n"/>
-      <c r="H38" s="38" t="n"/>
-      <c r="I38" s="38" t="n"/>
-      <c r="J38" s="38" t="n"/>
-      <c r="K38" s="38" t="n"/>
-      <c r="L38" s="38" t="n"/>
-      <c r="M38" s="38" t="n"/>
-      <c r="N38" s="38" t="n"/>
-      <c r="O38" s="38" t="n"/>
-      <c r="P38" s="47" t="n"/>
-    </row>
-    <row r="39" ht="19" customHeight="1" s="70">
-      <c r="A39" s="34" t="inlineStr">
+      <c r="B38" s="98" t="n"/>
+      <c r="C38" s="98" t="n"/>
+      <c r="D38" s="98" t="n"/>
+      <c r="E38" s="98" t="n"/>
+      <c r="F38" s="98" t="n"/>
+      <c r="G38" s="98" t="n"/>
+      <c r="H38" s="98" t="n"/>
+      <c r="I38" s="98" t="n"/>
+      <c r="J38" s="98" t="n"/>
+      <c r="K38" s="98" t="n"/>
+      <c r="L38" s="98" t="n"/>
+      <c r="M38" s="98" t="n"/>
+      <c r="N38" s="98" t="n"/>
+      <c r="O38" s="98" t="n"/>
+      <c r="P38" s="97" t="n"/>
+    </row>
+    <row r="39" ht="19.05" customHeight="1" s="127">
+      <c r="A39" s="74" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="74" t="inlineStr">
         <is>
           <t>Ene</t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C39" s="74" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D39" s="34" t="inlineStr">
+      <c r="D39" s="74" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E39" s="34" t="inlineStr">
+      <c r="E39" s="74" t="inlineStr">
         <is>
           <t>Abr</t>
         </is>
       </c>
-      <c r="F39" s="34" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G39" s="34" t="inlineStr">
+      <c r="G39" s="74" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H39" s="34" t="inlineStr">
+      <c r="H39" s="74" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I39" s="34" t="inlineStr">
+      <c r="I39" s="74" t="inlineStr">
         <is>
           <t>Ago</t>
         </is>
       </c>
-      <c r="J39" s="34" t="inlineStr">
+      <c r="J39" s="74" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K39" s="34" t="inlineStr">
+      <c r="K39" s="74" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L39" s="34" t="inlineStr">
+      <c r="L39" s="74" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M39" s="34" t="inlineStr">
+      <c r="M39" s="74" t="inlineStr">
         <is>
           <t>Dic</t>
         </is>
       </c>
-      <c r="N39" s="34" t="inlineStr">
+      <c r="N39" s="74" t="inlineStr">
         <is>
           <t>Año (acum.)</t>
         </is>
       </c>
-      <c r="O39" s="34" t="inlineStr">
+      <c r="O39" s="74" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="P39" s="31" t="n"/>
-    </row>
-    <row r="40" ht="17" customHeight="1" s="70">
-      <c r="A40" s="117" t="inlineStr">
+      <c r="P39" s="89" t="n"/>
+    </row>
+    <row r="40" ht="16.95" customHeight="1" s="127">
+      <c r="A40" s="52" t="inlineStr">
         <is>
           <t>Capacitaciones programadas</t>
         </is>
       </c>
-      <c r="B40" s="57" t="n"/>
-      <c r="C40" s="57" t="n"/>
-      <c r="D40" s="57" t="n"/>
-      <c r="E40" s="57" t="n"/>
-      <c r="F40" s="57" t="n"/>
-      <c r="G40" s="57" t="n"/>
-      <c r="H40" s="57" t="n"/>
-      <c r="I40" s="57" t="n"/>
-      <c r="J40" s="57" t="n"/>
-      <c r="K40" s="57" t="n"/>
-      <c r="L40" s="57" t="n"/>
-      <c r="M40" s="57" t="n"/>
-      <c r="N40" s="119">
+      <c r="B40" s="126" t="n"/>
+      <c r="C40" s="126" t="n"/>
+      <c r="D40" s="126" t="n"/>
+      <c r="E40" s="126" t="n"/>
+      <c r="F40" s="126" t="n"/>
+      <c r="G40" s="126" t="n"/>
+      <c r="H40" s="126" t="n"/>
+      <c r="I40" s="126" t="n"/>
+      <c r="J40" s="126" t="n"/>
+      <c r="K40" s="126" t="n"/>
+      <c r="L40" s="126" t="n"/>
+      <c r="M40" s="126" t="n"/>
+      <c r="N40" s="176">
         <f>IF(COUNT(B40:M40)=0,"",SUM(B40:M40))</f>
         <v/>
       </c>
-      <c r="O40" s="57" t="n"/>
-      <c r="P40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="17" customHeight="1" s="70">
-      <c r="A41" s="117" t="inlineStr">
+      <c r="O40" s="126" t="n"/>
+      <c r="P40" s="89" t="n"/>
+    </row>
+    <row r="41" ht="16.95" customHeight="1" s="127">
+      <c r="A41" s="52" t="inlineStr">
         <is>
           <t>Capacitaciones ejecutadas</t>
         </is>
       </c>
-      <c r="B41" s="57" t="n"/>
-      <c r="C41" s="57" t="n"/>
-      <c r="D41" s="57" t="n"/>
-      <c r="E41" s="57" t="n"/>
-      <c r="F41" s="57" t="n"/>
-      <c r="G41" s="57" t="n"/>
-      <c r="H41" s="57" t="n"/>
-      <c r="I41" s="57" t="n"/>
-      <c r="J41" s="57" t="n"/>
-      <c r="K41" s="57" t="n"/>
-      <c r="L41" s="57" t="n"/>
-      <c r="M41" s="57" t="n"/>
-      <c r="N41" s="119">
+      <c r="B41" s="126" t="n"/>
+      <c r="C41" s="126" t="n"/>
+      <c r="D41" s="126" t="n"/>
+      <c r="E41" s="126" t="n"/>
+      <c r="F41" s="126" t="n"/>
+      <c r="G41" s="126" t="n"/>
+      <c r="H41" s="126" t="n"/>
+      <c r="I41" s="126" t="n"/>
+      <c r="J41" s="126" t="n"/>
+      <c r="K41" s="126" t="n"/>
+      <c r="L41" s="126" t="n"/>
+      <c r="M41" s="126" t="n"/>
+      <c r="N41" s="176">
         <f>IF(COUNT(B41:M41)=0,"",SUM(B41:M41))</f>
         <v/>
       </c>
-      <c r="O41" s="57" t="n"/>
-      <c r="P41" s="31" t="n"/>
-    </row>
-    <row r="42" ht="17" customHeight="1" s="70">
-      <c r="A42" s="121" t="inlineStr">
+      <c r="O41" s="126" t="n"/>
+      <c r="P41" s="89" t="n"/>
+    </row>
+    <row r="42" ht="16.95" customHeight="1" s="127">
+      <c r="A42" s="54" t="inlineStr">
         <is>
           <t>Cumplimiento del plan de capacitación (%)</t>
         </is>
       </c>
-      <c r="B42" s="122">
+      <c r="B42" s="55">
         <f>IFERROR(IF(OR(B40="",B40=0,B41=""),"",B41/B40),"")</f>
         <v/>
       </c>
-      <c r="C42" s="122">
+      <c r="C42" s="55">
         <f>IFERROR(IF(OR(C40="",C40=0,C41=""),"",C41/C40),"")</f>
         <v/>
       </c>
-      <c r="D42" s="122">
+      <c r="D42" s="55">
         <f>IFERROR(IF(OR(D40="",D40=0,D41=""),"",D41/D40),"")</f>
         <v/>
       </c>
-      <c r="E42" s="122">
+      <c r="E42" s="55">
         <f>IFERROR(IF(OR(E40="",E40=0,E41=""),"",E41/E40),"")</f>
         <v/>
       </c>
-      <c r="F42" s="122">
+      <c r="F42" s="55">
         <f>IFERROR(IF(OR(F40="",F40=0,F41=""),"",F41/F40),"")</f>
         <v/>
       </c>
-      <c r="G42" s="122">
+      <c r="G42" s="55">
         <f>IFERROR(IF(OR(G40="",G40=0,G41=""),"",G41/G40),"")</f>
         <v/>
       </c>
-      <c r="H42" s="122">
+      <c r="H42" s="55">
         <f>IFERROR(IF(OR(H40="",H40=0,H41=""),"",H41/H40),"")</f>
         <v/>
       </c>
-      <c r="I42" s="122">
+      <c r="I42" s="55">
         <f>IFERROR(IF(OR(I40="",I40=0,I41=""),"",I41/I40),"")</f>
         <v/>
       </c>
-      <c r="J42" s="122">
+      <c r="J42" s="55">
         <f>IFERROR(IF(OR(J40="",J40=0,J41=""),"",J41/J40),"")</f>
         <v/>
       </c>
-      <c r="K42" s="122">
+      <c r="K42" s="55">
         <f>IFERROR(IF(OR(K40="",K40=0,K41=""),"",K41/K40),"")</f>
         <v/>
       </c>
-      <c r="L42" s="122">
+      <c r="L42" s="55">
         <f>IFERROR(IF(OR(L40="",L40=0,L41=""),"",L41/L40),"")</f>
         <v/>
       </c>
-      <c r="M42" s="122">
+      <c r="M42" s="55">
         <f>IFERROR(IF(OR(M40="",M40=0,M41=""),"",M41/M40),"")</f>
         <v/>
       </c>
-      <c r="N42" s="122">
+      <c r="N42" s="55">
         <f>IFERROR(IF(OR(N40="",N40=0,N41=""),"",N41/N40),"")</f>
         <v/>
       </c>
-      <c r="O42" s="57" t="n"/>
-      <c r="P42" s="31" t="n"/>
-    </row>
-    <row r="43" ht="17" customHeight="1" s="70">
-      <c r="A43" s="117" t="inlineStr">
+      <c r="O42" s="126" t="n"/>
+      <c r="P42" s="89" t="n"/>
+    </row>
+    <row r="43" ht="16.95" customHeight="1" s="127">
+      <c r="A43" s="52" t="inlineStr">
         <is>
           <t>Inspecciones programadas</t>
         </is>
       </c>
-      <c r="B43" s="57" t="n"/>
-      <c r="C43" s="57" t="n"/>
-      <c r="D43" s="57" t="n"/>
-      <c r="E43" s="57" t="n"/>
-      <c r="F43" s="57" t="n"/>
-      <c r="G43" s="57" t="n"/>
-      <c r="H43" s="57" t="n"/>
-      <c r="I43" s="57" t="n"/>
-      <c r="J43" s="57" t="n"/>
-      <c r="K43" s="57" t="n"/>
-      <c r="L43" s="57" t="n"/>
-      <c r="M43" s="57" t="n"/>
-      <c r="N43" s="119">
+      <c r="B43" s="126" t="n"/>
+      <c r="C43" s="126" t="n"/>
+      <c r="D43" s="126" t="n"/>
+      <c r="E43" s="126" t="n"/>
+      <c r="F43" s="126" t="n"/>
+      <c r="G43" s="126" t="n"/>
+      <c r="H43" s="126" t="n"/>
+      <c r="I43" s="126" t="n"/>
+      <c r="J43" s="126" t="n"/>
+      <c r="K43" s="126" t="n"/>
+      <c r="L43" s="126" t="n"/>
+      <c r="M43" s="126" t="n"/>
+      <c r="N43" s="176">
         <f>IF(COUNT(B43:M43)=0,"",SUM(B43:M43))</f>
         <v/>
       </c>
-      <c r="O43" s="57" t="n"/>
-      <c r="P43" s="31" t="n"/>
-    </row>
-    <row r="44" ht="17" customHeight="1" s="70">
-      <c r="A44" s="117" t="inlineStr">
+      <c r="O43" s="126" t="n"/>
+      <c r="P43" s="89" t="n"/>
+    </row>
+    <row r="44" ht="16.95" customHeight="1" s="127">
+      <c r="A44" s="52" t="inlineStr">
         <is>
           <t>Inspecciones ejecutadas</t>
         </is>
       </c>
-      <c r="B44" s="57" t="n"/>
-      <c r="C44" s="57" t="n"/>
-      <c r="D44" s="57" t="n"/>
-      <c r="E44" s="57" t="n"/>
-      <c r="F44" s="57" t="n"/>
-      <c r="G44" s="57" t="n"/>
-      <c r="H44" s="57" t="n"/>
-      <c r="I44" s="57" t="n"/>
-      <c r="J44" s="57" t="n"/>
-      <c r="K44" s="57" t="n"/>
-      <c r="L44" s="57" t="n"/>
-      <c r="M44" s="57" t="n"/>
-      <c r="N44" s="119">
+      <c r="B44" s="126" t="n"/>
+      <c r="C44" s="126" t="n"/>
+      <c r="D44" s="126" t="n"/>
+      <c r="E44" s="126" t="n"/>
+      <c r="F44" s="126" t="n"/>
+      <c r="G44" s="126" t="n"/>
+      <c r="H44" s="126" t="n"/>
+      <c r="I44" s="126" t="n"/>
+      <c r="J44" s="126" t="n"/>
+      <c r="K44" s="126" t="n"/>
+      <c r="L44" s="126" t="n"/>
+      <c r="M44" s="126" t="n"/>
+      <c r="N44" s="176">
         <f>IF(COUNT(B44:M44)=0,"",SUM(B44:M44))</f>
         <v/>
       </c>
-      <c r="O44" s="57" t="n"/>
-      <c r="P44" s="31" t="n"/>
-    </row>
-    <row r="45" ht="17" customHeight="1" s="70">
-      <c r="A45" s="121" t="inlineStr">
+      <c r="O44" s="126" t="n"/>
+      <c r="P44" s="89" t="n"/>
+    </row>
+    <row r="45" ht="16.95" customHeight="1" s="127">
+      <c r="A45" s="54" t="inlineStr">
         <is>
           <t>Cumplimiento del plan de inspecciones (%)</t>
         </is>
       </c>
-      <c r="B45" s="122">
+      <c r="B45" s="55">
         <f>IFERROR(IF(OR(B43="",B43=0,B44=""),"",B44/B43),"")</f>
         <v/>
       </c>
-      <c r="C45" s="122">
+      <c r="C45" s="55">
         <f>IFERROR(IF(OR(C43="",C43=0,C44=""),"",C44/C43),"")</f>
         <v/>
       </c>
-      <c r="D45" s="122">
+      <c r="D45" s="55">
         <f>IFERROR(IF(OR(D43="",D43=0,D44=""),"",D44/D43),"")</f>
         <v/>
       </c>
-      <c r="E45" s="122">
+      <c r="E45" s="55">
         <f>IFERROR(IF(OR(E43="",E43=0,E44=""),"",E44/E43),"")</f>
         <v/>
       </c>
-      <c r="F45" s="122">
+      <c r="F45" s="55">
         <f>IFERROR(IF(OR(F43="",F43=0,F44=""),"",F44/F43),"")</f>
         <v/>
       </c>
-      <c r="G45" s="122">
+      <c r="G45" s="55">
         <f>IFERROR(IF(OR(G43="",G43=0,G44=""),"",G44/G43),"")</f>
         <v/>
       </c>
-      <c r="H45" s="122">
+      <c r="H45" s="55">
         <f>IFERROR(IF(OR(H43="",H43=0,H44=""),"",H44/H43),"")</f>
         <v/>
       </c>
-      <c r="I45" s="122">
+      <c r="I45" s="55">
         <f>IFERROR(IF(OR(I43="",I43=0,I44=""),"",I44/I43),"")</f>
         <v/>
       </c>
-      <c r="J45" s="122">
+      <c r="J45" s="55">
         <f>IFERROR(IF(OR(J43="",J43=0,J44=""),"",J44/J43),"")</f>
         <v/>
       </c>
-      <c r="K45" s="122">
+      <c r="K45" s="55">
         <f>IFERROR(IF(OR(K43="",K43=0,K44=""),"",K44/K43),"")</f>
         <v/>
       </c>
-      <c r="L45" s="122">
+      <c r="L45" s="55">
         <f>IFERROR(IF(OR(L43="",L43=0,L44=""),"",L44/L43),"")</f>
         <v/>
       </c>
-      <c r="M45" s="122">
+      <c r="M45" s="55">
         <f>IFERROR(IF(OR(M43="",M43=0,M44=""),"",M44/M43),"")</f>
         <v/>
       </c>
-      <c r="N45" s="122">
+      <c r="N45" s="55">
         <f>IFERROR(IF(OR(N43="",N43=0,N44=""),"",N44/N43),"")</f>
         <v/>
       </c>
-      <c r="O45" s="57" t="n"/>
-      <c r="P45" s="31" t="n"/>
-    </row>
-    <row r="46" ht="17" customHeight="1" s="70">
-      <c r="A46" s="117" t="inlineStr">
+      <c r="O45" s="126" t="n"/>
+      <c r="P45" s="89" t="n"/>
+    </row>
+    <row r="46" ht="16.95" customHeight="1" s="127">
+      <c r="A46" s="52" t="inlineStr">
         <is>
           <t>Acciones correctivas abiertas en el mes</t>
         </is>
       </c>
-      <c r="B46" s="57" t="n"/>
-      <c r="C46" s="57" t="n"/>
-      <c r="D46" s="57" t="n"/>
-      <c r="E46" s="57" t="n"/>
-      <c r="F46" s="57" t="n"/>
-      <c r="G46" s="57" t="n"/>
-      <c r="H46" s="57" t="n"/>
-      <c r="I46" s="57" t="n"/>
-      <c r="J46" s="57" t="n"/>
-      <c r="K46" s="57" t="n"/>
-      <c r="L46" s="57" t="n"/>
-      <c r="M46" s="57" t="n"/>
-      <c r="N46" s="119">
+      <c r="B46" s="126" t="n"/>
+      <c r="C46" s="126" t="n"/>
+      <c r="D46" s="126" t="n"/>
+      <c r="E46" s="126" t="n"/>
+      <c r="F46" s="126" t="n"/>
+      <c r="G46" s="126" t="n"/>
+      <c r="H46" s="126" t="n"/>
+      <c r="I46" s="126" t="n"/>
+      <c r="J46" s="126" t="n"/>
+      <c r="K46" s="126" t="n"/>
+      <c r="L46" s="126" t="n"/>
+      <c r="M46" s="126" t="n"/>
+      <c r="N46" s="176">
         <f>IF(COUNT(B46:M46)=0,"",SUM(B46:M46))</f>
         <v/>
       </c>
-      <c r="O46" s="57" t="n"/>
-      <c r="P46" s="31" t="n"/>
-    </row>
-    <row r="47" ht="17" customHeight="1" s="70">
-      <c r="A47" s="117" t="inlineStr">
+      <c r="O46" s="126" t="n"/>
+      <c r="P46" s="89" t="n"/>
+    </row>
+    <row r="47" ht="16.95" customHeight="1" s="127">
+      <c r="A47" s="52" t="inlineStr">
         <is>
           <t>Acciones correctivas cerradas en el mes</t>
         </is>
       </c>
-      <c r="B47" s="57" t="n"/>
-      <c r="C47" s="57" t="n"/>
-      <c r="D47" s="57" t="n"/>
-      <c r="E47" s="57" t="n"/>
-      <c r="F47" s="57" t="n"/>
-      <c r="G47" s="57" t="n"/>
-      <c r="H47" s="57" t="n"/>
-      <c r="I47" s="57" t="n"/>
-      <c r="J47" s="57" t="n"/>
-      <c r="K47" s="57" t="n"/>
-      <c r="L47" s="57" t="n"/>
-      <c r="M47" s="57" t="n"/>
-      <c r="N47" s="119">
+      <c r="B47" s="126" t="n"/>
+      <c r="C47" s="126" t="n"/>
+      <c r="D47" s="126" t="n"/>
+      <c r="E47" s="126" t="n"/>
+      <c r="F47" s="126" t="n"/>
+      <c r="G47" s="126" t="n"/>
+      <c r="H47" s="126" t="n"/>
+      <c r="I47" s="126" t="n"/>
+      <c r="J47" s="126" t="n"/>
+      <c r="K47" s="126" t="n"/>
+      <c r="L47" s="126" t="n"/>
+      <c r="M47" s="126" t="n"/>
+      <c r="N47" s="176">
         <f>IF(COUNT(B47:M47)=0,"",SUM(B47:M47))</f>
         <v/>
       </c>
-      <c r="O47" s="57" t="n"/>
-      <c r="P47" s="31" t="n"/>
-    </row>
-    <row r="48" ht="17" customHeight="1" s="70">
-      <c r="A48" s="121" t="inlineStr">
+      <c r="O47" s="126" t="n"/>
+      <c r="P47" s="89" t="n"/>
+    </row>
+    <row r="48" ht="16.95" customHeight="1" s="127">
+      <c r="A48" s="54" t="inlineStr">
         <is>
           <t>Cierre de acciones correctivas (%)</t>
         </is>
       </c>
-      <c r="B48" s="122">
+      <c r="B48" s="55">
         <f>IFERROR(IF(OR(B46="",B46=0,B47=""),"",B47/B46),"")</f>
         <v/>
       </c>
-      <c r="C48" s="122">
+      <c r="C48" s="55">
         <f>IFERROR(IF(OR(C46="",C46=0,C47=""),"",C47/C46),"")</f>
         <v/>
       </c>
-      <c r="D48" s="122">
+      <c r="D48" s="55">
         <f>IFERROR(IF(OR(D46="",D46=0,D47=""),"",D47/D46),"")</f>
         <v/>
       </c>
-      <c r="E48" s="122">
+      <c r="E48" s="55">
         <f>IFERROR(IF(OR(E46="",E46=0,E47=""),"",E47/E46),"")</f>
         <v/>
       </c>
-      <c r="F48" s="122">
+      <c r="F48" s="55">
         <f>IFERROR(IF(OR(F46="",F46=0,F47=""),"",F47/F46),"")</f>
         <v/>
       </c>
-      <c r="G48" s="122">
+      <c r="G48" s="55">
         <f>IFERROR(IF(OR(G46="",G46=0,G47=""),"",G47/G46),"")</f>
         <v/>
       </c>
-      <c r="H48" s="122">
+      <c r="H48" s="55">
         <f>IFERROR(IF(OR(H46="",H46=0,H47=""),"",H47/H46),"")</f>
         <v/>
       </c>
-      <c r="I48" s="122">
+      <c r="I48" s="55">
         <f>IFERROR(IF(OR(I46="",I46=0,I47=""),"",I47/I46),"")</f>
         <v/>
       </c>
-      <c r="J48" s="122">
+      <c r="J48" s="55">
         <f>IFERROR(IF(OR(J46="",J46=0,J47=""),"",J47/J46),"")</f>
         <v/>
       </c>
-      <c r="K48" s="122">
+      <c r="K48" s="55">
         <f>IFERROR(IF(OR(K46="",K46=0,K47=""),"",K47/K46),"")</f>
         <v/>
       </c>
-      <c r="L48" s="122">
+      <c r="L48" s="55">
         <f>IFERROR(IF(OR(L46="",L46=0,L47=""),"",L47/L46),"")</f>
         <v/>
       </c>
-      <c r="M48" s="122">
+      <c r="M48" s="55">
         <f>IFERROR(IF(OR(M46="",M46=0,M47=""),"",M47/M46),"")</f>
         <v/>
       </c>
-      <c r="N48" s="122">
+      <c r="N48" s="55">
         <f>IFERROR(IF(OR(N46="",N46=0,N47=""),"",N47/N46),"")</f>
         <v/>
       </c>
-      <c r="O48" s="57" t="n"/>
-      <c r="P48" s="31" t="n"/>
-    </row>
-    <row r="49" ht="17" customHeight="1" s="70">
-      <c r="A49" s="117" t="inlineStr">
+      <c r="O48" s="126" t="n"/>
+      <c r="P48" s="89" t="n"/>
+    </row>
+    <row r="49" ht="16.95" customHeight="1" s="127">
+      <c r="A49" s="52" t="inlineStr">
         <is>
           <t>Actos y condiciones inseguras reportados (N°)</t>
         </is>
       </c>
-      <c r="B49" s="57" t="n"/>
-      <c r="C49" s="57" t="n"/>
-      <c r="D49" s="57" t="n"/>
-      <c r="E49" s="57" t="n"/>
-      <c r="F49" s="57" t="n"/>
-      <c r="G49" s="57" t="n"/>
-      <c r="H49" s="57" t="n"/>
-      <c r="I49" s="57" t="n"/>
-      <c r="J49" s="57" t="n"/>
-      <c r="K49" s="57" t="n"/>
-      <c r="L49" s="57" t="n"/>
-      <c r="M49" s="57" t="n"/>
-      <c r="N49" s="119">
+      <c r="B49" s="126" t="n"/>
+      <c r="C49" s="126" t="n"/>
+      <c r="D49" s="126" t="n"/>
+      <c r="E49" s="126" t="n"/>
+      <c r="F49" s="126" t="n"/>
+      <c r="G49" s="126" t="n"/>
+      <c r="H49" s="126" t="n"/>
+      <c r="I49" s="126" t="n"/>
+      <c r="J49" s="126" t="n"/>
+      <c r="K49" s="126" t="n"/>
+      <c r="L49" s="126" t="n"/>
+      <c r="M49" s="126" t="n"/>
+      <c r="N49" s="176">
         <f>IF(COUNT(B49:M49)=0,"",SUM(B49:M49))</f>
         <v/>
       </c>
-      <c r="O49" s="57" t="n"/>
-      <c r="P49" s="31" t="n"/>
-    </row>
-    <row r="50" ht="16.5" customHeight="1" s="70">
-      <c r="A50" s="54" t="inlineStr">
+      <c r="O49" s="126" t="n"/>
+      <c r="P49" s="89" t="n"/>
+    </row>
+    <row r="50" ht="16.5" customHeight="1" s="127">
+      <c r="A50" s="137" t="inlineStr">
         <is>
           <t>ANÁLISIS Y DECISIONES</t>
         </is>
       </c>
-      <c r="B50" s="38" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="38" t="n"/>
-      <c r="E50" s="38" t="n"/>
-      <c r="F50" s="38" t="n"/>
-      <c r="G50" s="38" t="n"/>
-      <c r="H50" s="38" t="n"/>
-      <c r="I50" s="38" t="n"/>
-      <c r="J50" s="38" t="n"/>
-      <c r="K50" s="38" t="n"/>
-      <c r="L50" s="38" t="n"/>
-      <c r="M50" s="38" t="n"/>
-      <c r="N50" s="38" t="n"/>
-      <c r="O50" s="38" t="n"/>
-      <c r="P50" s="47" t="n"/>
-    </row>
-    <row r="51" ht="30" customHeight="1" s="70">
-      <c r="A51" s="52" t="n"/>
-      <c r="B51" s="56" t="n"/>
-      <c r="C51" s="56" t="n"/>
-      <c r="D51" s="56" t="n"/>
-      <c r="E51" s="56" t="n"/>
-      <c r="F51" s="56" t="n"/>
-      <c r="G51" s="56" t="n"/>
-      <c r="H51" s="56" t="n"/>
-      <c r="I51" s="56" t="n"/>
-      <c r="J51" s="56" t="n"/>
-      <c r="K51" s="56" t="n"/>
-      <c r="L51" s="56" t="n"/>
-      <c r="M51" s="56" t="n"/>
-      <c r="N51" s="56" t="n"/>
-      <c r="O51" s="56" t="n"/>
-      <c r="P51" s="45" t="n"/>
-    </row>
-    <row r="52" ht="30" customHeight="1" s="70">
-      <c r="A52" s="46" t="n"/>
-      <c r="P52" s="41" t="n"/>
-    </row>
-    <row r="53" ht="30" customHeight="1" s="70">
-      <c r="A53" s="46" t="n"/>
-      <c r="P53" s="41" t="n"/>
-    </row>
-    <row r="54" ht="30" customHeight="1" s="70">
-      <c r="A54" s="46" t="n"/>
-      <c r="P54" s="41" t="n"/>
-    </row>
-    <row r="55" ht="30" customHeight="1" s="70">
-      <c r="A55" s="37" t="n"/>
-      <c r="B55" s="38" t="n"/>
-      <c r="C55" s="38" t="n"/>
-      <c r="D55" s="38" t="n"/>
-      <c r="E55" s="38" t="n"/>
-      <c r="F55" s="38" t="n"/>
-      <c r="G55" s="38" t="n"/>
-      <c r="H55" s="38" t="n"/>
-      <c r="I55" s="38" t="n"/>
-      <c r="J55" s="38" t="n"/>
-      <c r="K55" s="38" t="n"/>
-      <c r="L55" s="38" t="n"/>
-      <c r="M55" s="38" t="n"/>
-      <c r="N55" s="38" t="n"/>
-      <c r="O55" s="38" t="n"/>
-      <c r="P55" s="47" t="n"/>
-    </row>
-    <row r="56" ht="16.5" customHeight="1" s="70">
-      <c r="A56" s="54" t="inlineStr">
+      <c r="B50" s="98" t="n"/>
+      <c r="C50" s="98" t="n"/>
+      <c r="D50" s="98" t="n"/>
+      <c r="E50" s="98" t="n"/>
+      <c r="F50" s="98" t="n"/>
+      <c r="G50" s="98" t="n"/>
+      <c r="H50" s="98" t="n"/>
+      <c r="I50" s="98" t="n"/>
+      <c r="J50" s="98" t="n"/>
+      <c r="K50" s="98" t="n"/>
+      <c r="L50" s="98" t="n"/>
+      <c r="M50" s="98" t="n"/>
+      <c r="N50" s="98" t="n"/>
+      <c r="O50" s="98" t="n"/>
+      <c r="P50" s="97" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1" s="127">
+      <c r="A51" s="100" t="n"/>
+      <c r="B51" s="104" t="n"/>
+      <c r="C51" s="104" t="n"/>
+      <c r="D51" s="104" t="n"/>
+      <c r="E51" s="104" t="n"/>
+      <c r="F51" s="104" t="n"/>
+      <c r="G51" s="104" t="n"/>
+      <c r="H51" s="104" t="n"/>
+      <c r="I51" s="104" t="n"/>
+      <c r="J51" s="104" t="n"/>
+      <c r="K51" s="104" t="n"/>
+      <c r="L51" s="104" t="n"/>
+      <c r="M51" s="104" t="n"/>
+      <c r="N51" s="104" t="n"/>
+      <c r="O51" s="104" t="n"/>
+      <c r="P51" s="94" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1" s="127">
+      <c r="A52" s="95" t="n"/>
+      <c r="P52" s="92" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1" s="127">
+      <c r="A53" s="95" t="n"/>
+      <c r="P53" s="92" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1" s="127">
+      <c r="A54" s="95" t="n"/>
+      <c r="P54" s="92" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1" s="127">
+      <c r="A55" s="96" t="n"/>
+      <c r="B55" s="98" t="n"/>
+      <c r="C55" s="98" t="n"/>
+      <c r="D55" s="98" t="n"/>
+      <c r="E55" s="98" t="n"/>
+      <c r="F55" s="98" t="n"/>
+      <c r="G55" s="98" t="n"/>
+      <c r="H55" s="98" t="n"/>
+      <c r="I55" s="98" t="n"/>
+      <c r="J55" s="98" t="n"/>
+      <c r="K55" s="98" t="n"/>
+      <c r="L55" s="98" t="n"/>
+      <c r="M55" s="98" t="n"/>
+      <c r="N55" s="98" t="n"/>
+      <c r="O55" s="98" t="n"/>
+      <c r="P55" s="97" t="n"/>
+    </row>
+    <row r="56" ht="16.5" customHeight="1" s="127">
+      <c r="A56" s="137" t="inlineStr">
         <is>
           <t>FIRMAS</t>
         </is>
       </c>
-      <c r="B56" s="38" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="38" t="n"/>
-      <c r="E56" s="38" t="n"/>
-      <c r="F56" s="38" t="n"/>
-      <c r="G56" s="38" t="n"/>
-      <c r="H56" s="38" t="n"/>
-      <c r="I56" s="38" t="n"/>
-      <c r="J56" s="38" t="n"/>
-      <c r="K56" s="38" t="n"/>
-      <c r="L56" s="38" t="n"/>
-      <c r="M56" s="38" t="n"/>
-      <c r="N56" s="38" t="n"/>
-      <c r="O56" s="38" t="n"/>
-      <c r="P56" s="47" t="n"/>
-    </row>
-    <row r="57" ht="18" customHeight="1" s="70">
-      <c r="A57" s="123" t="inlineStr">
+      <c r="B56" s="98" t="n"/>
+      <c r="C56" s="98" t="n"/>
+      <c r="D56" s="98" t="n"/>
+      <c r="E56" s="98" t="n"/>
+      <c r="F56" s="98" t="n"/>
+      <c r="G56" s="98" t="n"/>
+      <c r="H56" s="98" t="n"/>
+      <c r="I56" s="98" t="n"/>
+      <c r="J56" s="98" t="n"/>
+      <c r="K56" s="98" t="n"/>
+      <c r="L56" s="98" t="n"/>
+      <c r="M56" s="98" t="n"/>
+      <c r="N56" s="98" t="n"/>
+      <c r="O56" s="98" t="n"/>
+      <c r="P56" s="97" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1" s="127">
+      <c r="A57" s="359" t="inlineStr">
         <is>
           <t>Firmas del informe</t>
         </is>
       </c>
-      <c r="B57" s="51" t="inlineStr">
+      <c r="B57" s="261" t="inlineStr">
         <is>
           <t>ELABORÓ — RESPONSABLE SST</t>
         </is>
       </c>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="30" t="n"/>
-      <c r="E57" s="31" t="n"/>
-      <c r="F57" s="51" t="inlineStr">
+      <c r="C57" s="347" t="n"/>
+      <c r="D57" s="347" t="n"/>
+      <c r="E57" s="348" t="n"/>
+      <c r="F57" s="261" t="inlineStr">
         <is>
           <t>REVISÓ — RESIDENTE DE OBRA</t>
         </is>
       </c>
-      <c r="G57" s="30" t="n"/>
-      <c r="H57" s="30" t="n"/>
-      <c r="I57" s="30" t="n"/>
-      <c r="J57" s="31" t="n"/>
-      <c r="K57" s="51" t="inlineStr">
+      <c r="G57" s="347" t="n"/>
+      <c r="H57" s="347" t="n"/>
+      <c r="I57" s="347" t="n"/>
+      <c r="J57" s="348" t="n"/>
+      <c r="K57" s="261" t="inlineStr">
         <is>
           <t>Vo.Bo. — GERENCIA / INTERVENTORÍA</t>
         </is>
       </c>
-      <c r="L57" s="30" t="n"/>
-      <c r="M57" s="30" t="n"/>
-      <c r="N57" s="30" t="n"/>
-      <c r="O57" s="30" t="n"/>
-      <c r="P57" s="31" t="n"/>
-    </row>
-    <row r="58" ht="42" customHeight="1" s="70">
-      <c r="A58" s="124" t="n"/>
-      <c r="B58" s="39" t="inlineStr">
+      <c r="L57" s="347" t="n"/>
+      <c r="M57" s="347" t="n"/>
+      <c r="N57" s="347" t="n"/>
+      <c r="O57" s="347" t="n"/>
+      <c r="P57" s="348" t="n"/>
+    </row>
+    <row r="58" ht="42" customHeight="1" s="127">
+      <c r="A58" s="131" t="n"/>
+      <c r="B58" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="43" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="39" t="inlineStr">
+      <c r="C58" s="97" t="n"/>
+      <c r="D58" s="301" t="n"/>
+      <c r="E58" s="97" t="n"/>
+      <c r="F58" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="43" t="n"/>
-      <c r="I58" s="30" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="39" t="inlineStr">
+      <c r="G58" s="97" t="n"/>
+      <c r="H58" s="301" t="n"/>
+      <c r="I58" s="98" t="n"/>
+      <c r="J58" s="97" t="n"/>
+      <c r="K58" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="43" t="n"/>
-      <c r="N58" s="30" t="n"/>
-      <c r="O58" s="30" t="n"/>
-      <c r="P58" s="31" t="n"/>
-    </row>
-    <row r="59" ht="21" customHeight="1" s="70">
-      <c r="A59" s="124" t="n"/>
-      <c r="B59" s="39" t="inlineStr">
+      <c r="L58" s="97" t="n"/>
+      <c r="M58" s="301" t="n"/>
+      <c r="N58" s="98" t="n"/>
+      <c r="O58" s="98" t="n"/>
+      <c r="P58" s="97" t="n"/>
+    </row>
+    <row r="59" ht="21" customHeight="1" s="127">
+      <c r="A59" s="131" t="n"/>
+      <c r="B59" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="C59" s="31" t="n"/>
-      <c r="D59" s="43" t="n"/>
-      <c r="E59" s="31" t="n"/>
-      <c r="F59" s="39" t="inlineStr">
+      <c r="C59" s="89" t="n"/>
+      <c r="D59" s="68" t="n"/>
+      <c r="E59" s="89" t="n"/>
+      <c r="F59" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="G59" s="31" t="n"/>
-      <c r="H59" s="43" t="n"/>
-      <c r="I59" s="30" t="n"/>
-      <c r="J59" s="31" t="n"/>
-      <c r="K59" s="39" t="inlineStr">
+      <c r="G59" s="89" t="n"/>
+      <c r="H59" s="68" t="n"/>
+      <c r="I59" s="93" t="n"/>
+      <c r="J59" s="89" t="n"/>
+      <c r="K59" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="L59" s="31" t="n"/>
-      <c r="M59" s="43" t="n"/>
-      <c r="N59" s="30" t="n"/>
-      <c r="O59" s="30" t="n"/>
-      <c r="P59" s="31" t="n"/>
-    </row>
-    <row r="60" ht="21" customHeight="1" s="70">
-      <c r="A60" s="125" t="n"/>
-      <c r="B60" s="39" t="inlineStr">
+      <c r="L59" s="89" t="n"/>
+      <c r="M59" s="68" t="n"/>
+      <c r="N59" s="93" t="n"/>
+      <c r="O59" s="93" t="n"/>
+      <c r="P59" s="89" t="n"/>
+    </row>
+    <row r="60" ht="21" customHeight="1" s="127">
+      <c r="A60" s="132" t="n"/>
+      <c r="B60" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="C60" s="31" t="n"/>
-      <c r="D60" s="43" t="n"/>
-      <c r="E60" s="31" t="n"/>
-      <c r="F60" s="39" t="inlineStr">
+      <c r="C60" s="89" t="n"/>
+      <c r="D60" s="68" t="n"/>
+      <c r="E60" s="89" t="n"/>
+      <c r="F60" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="G60" s="31" t="n"/>
-      <c r="H60" s="43" t="n"/>
-      <c r="I60" s="30" t="n"/>
-      <c r="J60" s="31" t="n"/>
-      <c r="K60" s="39" t="inlineStr">
+      <c r="G60" s="89" t="n"/>
+      <c r="H60" s="68" t="n"/>
+      <c r="I60" s="93" t="n"/>
+      <c r="J60" s="89" t="n"/>
+      <c r="K60" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="L60" s="31" t="n"/>
-      <c r="M60" s="43" t="n"/>
-      <c r="N60" s="30" t="n"/>
-      <c r="O60" s="30" t="n"/>
-      <c r="P60" s="31" t="n"/>
+      <c r="L60" s="89" t="n"/>
+      <c r="M60" s="68" t="n"/>
+      <c r="N60" s="93" t="n"/>
+      <c r="O60" s="93" t="n"/>
+      <c r="P60" s="89" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="61" t="inlineStr">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="I61" s="63">
+      <c r="I61" s="105">
         <f>O5</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="80">
+  <mergeCells count="83">
     <mergeCell ref="O7:P7"/>
     <mergeCell ref="D60:E60"/>
     <mergeCell ref="O6:P6"/>
-    <mergeCell ref="D3:P3"/>
     <mergeCell ref="O15:P15"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="A9:P9"/>
@@ -3276,6 +4373,7 @@
     <mergeCell ref="O41:P41"/>
     <mergeCell ref="O35:P35"/>
     <mergeCell ref="K58:L58"/>
+    <mergeCell ref="B6:M6"/>
     <mergeCell ref="O16:P16"/>
     <mergeCell ref="O25:P25"/>
     <mergeCell ref="O43:P43"/>
@@ -3284,19 +4382,21 @@
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="O17:P17"/>
+    <mergeCell ref="B7:M7"/>
     <mergeCell ref="H58:J58"/>
     <mergeCell ref="A26:P26"/>
-    <mergeCell ref="D1:P2"/>
     <mergeCell ref="H60:J60"/>
+    <mergeCell ref="B8:M8"/>
     <mergeCell ref="O45:P45"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D5:M5"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="O29:P29"/>
     <mergeCell ref="O44:P44"/>
     <mergeCell ref="O31:P31"/>
     <mergeCell ref="O21:P21"/>
+    <mergeCell ref="B5:M5"/>
     <mergeCell ref="M60:P60"/>
+    <mergeCell ref="B4:M4"/>
     <mergeCell ref="A57:A60"/>
     <mergeCell ref="A37:P37"/>
     <mergeCell ref="H59:J59"/>
@@ -3316,11 +4416,12 @@
     <mergeCell ref="O22:P22"/>
     <mergeCell ref="O46:P46"/>
     <mergeCell ref="M11:P11"/>
-    <mergeCell ref="D6:M6"/>
     <mergeCell ref="O47:P47"/>
     <mergeCell ref="A51:P55"/>
     <mergeCell ref="O48:P48"/>
     <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B1:P2"/>
+    <mergeCell ref="B3:P3"/>
     <mergeCell ref="O23:P23"/>
     <mergeCell ref="M12:P12"/>
     <mergeCell ref="A50:P50"/>
@@ -3346,7 +4447,7 @@
     <mergeCell ref="D59:E59"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 Página &amp;P de &amp;N</oddFooter>

--- a/public/plantilla-indicadores.xlsx
+++ b/public/plantilla-indicadores.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="39">
+  <numFmts count="0"/>
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -297,6 +298,15 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -1024,7 +1034,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="380">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1928,6 +1938,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2583,14 +2660,14 @@
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="161" t="n"/>
-      <c r="C11" s="93" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="89" t="n"/>
+      <c r="B11" s="360" t="n"/>
+      <c r="C11" s="361" t="n"/>
+      <c r="D11" s="361" t="n"/>
+      <c r="E11" s="361" t="n"/>
+      <c r="F11" s="361" t="n"/>
+      <c r="G11" s="361" t="n"/>
+      <c r="H11" s="361" t="n"/>
+      <c r="I11" s="362" t="n"/>
       <c r="J11" s="59" t="inlineStr">
         <is>
           <t>Año</t>
@@ -2598,10 +2675,10 @@
       </c>
       <c r="K11" s="93" t="n"/>
       <c r="L11" s="89" t="n"/>
-      <c r="M11" s="69" t="n"/>
-      <c r="N11" s="93" t="n"/>
-      <c r="O11" s="93" t="n"/>
-      <c r="P11" s="89" t="n"/>
+      <c r="M11" s="363" t="n"/>
+      <c r="N11" s="361" t="n"/>
+      <c r="O11" s="361" t="n"/>
+      <c r="P11" s="362" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2609,14 +2686,14 @@
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="B12" s="68" t="n"/>
-      <c r="C12" s="93" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="93" t="n"/>
-      <c r="H12" s="93" t="n"/>
-      <c r="I12" s="89" t="n"/>
+      <c r="B12" s="364" t="n"/>
+      <c r="C12" s="361" t="n"/>
+      <c r="D12" s="361" t="n"/>
+      <c r="E12" s="361" t="n"/>
+      <c r="F12" s="361" t="n"/>
+      <c r="G12" s="361" t="n"/>
+      <c r="H12" s="361" t="n"/>
+      <c r="I12" s="362" t="n"/>
       <c r="J12" s="59" t="inlineStr">
         <is>
           <t>Responsable</t>
@@ -2624,10 +2701,10 @@
       </c>
       <c r="K12" s="93" t="n"/>
       <c r="L12" s="89" t="n"/>
-      <c r="M12" s="68" t="n"/>
-      <c r="N12" s="93" t="n"/>
-      <c r="O12" s="93" t="n"/>
-      <c r="P12" s="89" t="n"/>
+      <c r="M12" s="364" t="n"/>
+      <c r="N12" s="361" t="n"/>
+      <c r="O12" s="361" t="n"/>
+      <c r="P12" s="362" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="127">
       <c r="A13" s="137" t="inlineStr">
@@ -2730,279 +2807,279 @@
       <c r="P14" s="89" t="n"/>
     </row>
     <row r="15" ht="16.95" customHeight="1" s="127">
-      <c r="A15" s="52" t="inlineStr">
+      <c r="A15" s="365" t="inlineStr">
         <is>
           <t>Promedio de trabajadores</t>
         </is>
       </c>
-      <c r="B15" s="126" t="n"/>
-      <c r="C15" s="126" t="n"/>
-      <c r="D15" s="126" t="n"/>
-      <c r="E15" s="126" t="n"/>
-      <c r="F15" s="126" t="n"/>
-      <c r="G15" s="126" t="n"/>
-      <c r="H15" s="126" t="n"/>
-      <c r="I15" s="126" t="n"/>
-      <c r="J15" s="126" t="n"/>
-      <c r="K15" s="126" t="n"/>
-      <c r="L15" s="126" t="n"/>
-      <c r="M15" s="126" t="n"/>
+      <c r="B15" s="366" t="n"/>
+      <c r="C15" s="366" t="n"/>
+      <c r="D15" s="366" t="n"/>
+      <c r="E15" s="366" t="n"/>
+      <c r="F15" s="366" t="n"/>
+      <c r="G15" s="366" t="n"/>
+      <c r="H15" s="366" t="n"/>
+      <c r="I15" s="366" t="n"/>
+      <c r="J15" s="366" t="n"/>
+      <c r="K15" s="366" t="n"/>
+      <c r="L15" s="366" t="n"/>
+      <c r="M15" s="366" t="n"/>
       <c r="N15" s="175">
         <f>IFERROR(AVERAGE(B15:M15),"")</f>
         <v/>
       </c>
-      <c r="O15" s="126" t="n"/>
-      <c r="P15" s="89" t="n"/>
+      <c r="O15" s="366" t="n"/>
+      <c r="P15" s="362" t="n"/>
     </row>
     <row r="16" ht="16.95" customHeight="1" s="127">
-      <c r="A16" s="52" t="inlineStr">
+      <c r="A16" s="365" t="inlineStr">
         <is>
           <t>Horas-hombre trabajadas (HHT)</t>
         </is>
       </c>
-      <c r="B16" s="126" t="n"/>
-      <c r="C16" s="126" t="n"/>
-      <c r="D16" s="126" t="n"/>
-      <c r="E16" s="126" t="n"/>
-      <c r="F16" s="126" t="n"/>
-      <c r="G16" s="126" t="n"/>
-      <c r="H16" s="126" t="n"/>
-      <c r="I16" s="126" t="n"/>
-      <c r="J16" s="126" t="n"/>
-      <c r="K16" s="126" t="n"/>
-      <c r="L16" s="126" t="n"/>
-      <c r="M16" s="126" t="n"/>
+      <c r="B16" s="366" t="n"/>
+      <c r="C16" s="366" t="n"/>
+      <c r="D16" s="366" t="n"/>
+      <c r="E16" s="366" t="n"/>
+      <c r="F16" s="366" t="n"/>
+      <c r="G16" s="366" t="n"/>
+      <c r="H16" s="366" t="n"/>
+      <c r="I16" s="366" t="n"/>
+      <c r="J16" s="366" t="n"/>
+      <c r="K16" s="366" t="n"/>
+      <c r="L16" s="366" t="n"/>
+      <c r="M16" s="366" t="n"/>
       <c r="N16" s="176">
         <f>IF(COUNT(B16:M16)=0,"",SUM(B16:M16))</f>
         <v/>
       </c>
-      <c r="O16" s="126" t="n"/>
-      <c r="P16" s="89" t="n"/>
+      <c r="O16" s="366" t="n"/>
+      <c r="P16" s="362" t="n"/>
     </row>
     <row r="17" ht="16.95" customHeight="1" s="127">
-      <c r="A17" s="52" t="inlineStr">
+      <c r="A17" s="365" t="inlineStr">
         <is>
           <t>Accidentes de trabajo (AT)</t>
         </is>
       </c>
-      <c r="B17" s="126" t="n"/>
-      <c r="C17" s="126" t="n"/>
-      <c r="D17" s="126" t="n"/>
-      <c r="E17" s="126" t="n"/>
-      <c r="F17" s="126" t="n"/>
-      <c r="G17" s="126" t="n"/>
-      <c r="H17" s="126" t="n"/>
-      <c r="I17" s="126" t="n"/>
-      <c r="J17" s="126" t="n"/>
-      <c r="K17" s="126" t="n"/>
-      <c r="L17" s="126" t="n"/>
-      <c r="M17" s="126" t="n"/>
+      <c r="B17" s="366" t="n"/>
+      <c r="C17" s="366" t="n"/>
+      <c r="D17" s="366" t="n"/>
+      <c r="E17" s="366" t="n"/>
+      <c r="F17" s="366" t="n"/>
+      <c r="G17" s="366" t="n"/>
+      <c r="H17" s="366" t="n"/>
+      <c r="I17" s="366" t="n"/>
+      <c r="J17" s="366" t="n"/>
+      <c r="K17" s="366" t="n"/>
+      <c r="L17" s="366" t="n"/>
+      <c r="M17" s="366" t="n"/>
       <c r="N17" s="176">
         <f>IF(COUNT(B17:M17)=0,"",SUM(B17:M17))</f>
         <v/>
       </c>
-      <c r="O17" s="126" t="n"/>
-      <c r="P17" s="89" t="n"/>
+      <c r="O17" s="366" t="n"/>
+      <c r="P17" s="362" t="n"/>
     </row>
     <row r="18" ht="16.95" customHeight="1" s="127">
-      <c r="A18" s="52" t="inlineStr">
+      <c r="A18" s="365" t="inlineStr">
         <is>
           <t>AT con incapacidad</t>
         </is>
       </c>
-      <c r="B18" s="126" t="n"/>
-      <c r="C18" s="126" t="n"/>
-      <c r="D18" s="126" t="n"/>
-      <c r="E18" s="126" t="n"/>
-      <c r="F18" s="126" t="n"/>
-      <c r="G18" s="126" t="n"/>
-      <c r="H18" s="126" t="n"/>
-      <c r="I18" s="126" t="n"/>
-      <c r="J18" s="126" t="n"/>
-      <c r="K18" s="126" t="n"/>
-      <c r="L18" s="126" t="n"/>
-      <c r="M18" s="126" t="n"/>
+      <c r="B18" s="366" t="n"/>
+      <c r="C18" s="366" t="n"/>
+      <c r="D18" s="366" t="n"/>
+      <c r="E18" s="366" t="n"/>
+      <c r="F18" s="366" t="n"/>
+      <c r="G18" s="366" t="n"/>
+      <c r="H18" s="366" t="n"/>
+      <c r="I18" s="366" t="n"/>
+      <c r="J18" s="366" t="n"/>
+      <c r="K18" s="366" t="n"/>
+      <c r="L18" s="366" t="n"/>
+      <c r="M18" s="366" t="n"/>
       <c r="N18" s="176">
         <f>IF(COUNT(B18:M18)=0,"",SUM(B18:M18))</f>
         <v/>
       </c>
-      <c r="O18" s="126" t="n"/>
-      <c r="P18" s="89" t="n"/>
+      <c r="O18" s="366" t="n"/>
+      <c r="P18" s="362" t="n"/>
     </row>
     <row r="19" ht="16.95" customHeight="1" s="127">
-      <c r="A19" s="52" t="inlineStr">
+      <c r="A19" s="365" t="inlineStr">
         <is>
           <t>Días de incapacidad por AT</t>
         </is>
       </c>
-      <c r="B19" s="126" t="n"/>
-      <c r="C19" s="126" t="n"/>
-      <c r="D19" s="126" t="n"/>
-      <c r="E19" s="126" t="n"/>
-      <c r="F19" s="126" t="n"/>
-      <c r="G19" s="126" t="n"/>
-      <c r="H19" s="126" t="n"/>
-      <c r="I19" s="126" t="n"/>
-      <c r="J19" s="126" t="n"/>
-      <c r="K19" s="126" t="n"/>
-      <c r="L19" s="126" t="n"/>
-      <c r="M19" s="126" t="n"/>
+      <c r="B19" s="366" t="n"/>
+      <c r="C19" s="366" t="n"/>
+      <c r="D19" s="366" t="n"/>
+      <c r="E19" s="366" t="n"/>
+      <c r="F19" s="366" t="n"/>
+      <c r="G19" s="366" t="n"/>
+      <c r="H19" s="366" t="n"/>
+      <c r="I19" s="366" t="n"/>
+      <c r="J19" s="366" t="n"/>
+      <c r="K19" s="366" t="n"/>
+      <c r="L19" s="366" t="n"/>
+      <c r="M19" s="366" t="n"/>
       <c r="N19" s="176">
         <f>IF(COUNT(B19:M19)=0,"",SUM(B19:M19))</f>
         <v/>
       </c>
-      <c r="O19" s="126" t="n"/>
-      <c r="P19" s="89" t="n"/>
+      <c r="O19" s="366" t="n"/>
+      <c r="P19" s="362" t="n"/>
     </row>
     <row r="20" ht="16.95" customHeight="1" s="127">
-      <c r="A20" s="52" t="inlineStr">
+      <c r="A20" s="365" t="inlineStr">
         <is>
           <t>AT mortales</t>
         </is>
       </c>
-      <c r="B20" s="126" t="n"/>
-      <c r="C20" s="126" t="n"/>
-      <c r="D20" s="126" t="n"/>
-      <c r="E20" s="126" t="n"/>
-      <c r="F20" s="126" t="n"/>
-      <c r="G20" s="126" t="n"/>
-      <c r="H20" s="126" t="n"/>
-      <c r="I20" s="126" t="n"/>
-      <c r="J20" s="126" t="n"/>
-      <c r="K20" s="126" t="n"/>
-      <c r="L20" s="126" t="n"/>
-      <c r="M20" s="126" t="n"/>
+      <c r="B20" s="366" t="n"/>
+      <c r="C20" s="366" t="n"/>
+      <c r="D20" s="366" t="n"/>
+      <c r="E20" s="366" t="n"/>
+      <c r="F20" s="366" t="n"/>
+      <c r="G20" s="366" t="n"/>
+      <c r="H20" s="366" t="n"/>
+      <c r="I20" s="366" t="n"/>
+      <c r="J20" s="366" t="n"/>
+      <c r="K20" s="366" t="n"/>
+      <c r="L20" s="366" t="n"/>
+      <c r="M20" s="366" t="n"/>
       <c r="N20" s="176">
         <f>IF(COUNT(B20:M20)=0,"",SUM(B20:M20))</f>
         <v/>
       </c>
-      <c r="O20" s="126" t="n"/>
-      <c r="P20" s="89" t="n"/>
+      <c r="O20" s="366" t="n"/>
+      <c r="P20" s="362" t="n"/>
     </row>
     <row r="21" ht="16.95" customHeight="1" s="127">
-      <c r="A21" s="52" t="inlineStr">
+      <c r="A21" s="365" t="inlineStr">
         <is>
           <t>Casos nuevos de enfermedad laboral</t>
         </is>
       </c>
-      <c r="B21" s="126" t="n"/>
-      <c r="C21" s="126" t="n"/>
-      <c r="D21" s="126" t="n"/>
-      <c r="E21" s="126" t="n"/>
-      <c r="F21" s="126" t="n"/>
-      <c r="G21" s="126" t="n"/>
-      <c r="H21" s="126" t="n"/>
-      <c r="I21" s="126" t="n"/>
-      <c r="J21" s="126" t="n"/>
-      <c r="K21" s="126" t="n"/>
-      <c r="L21" s="126" t="n"/>
-      <c r="M21" s="126" t="n"/>
+      <c r="B21" s="366" t="n"/>
+      <c r="C21" s="366" t="n"/>
+      <c r="D21" s="366" t="n"/>
+      <c r="E21" s="366" t="n"/>
+      <c r="F21" s="366" t="n"/>
+      <c r="G21" s="366" t="n"/>
+      <c r="H21" s="366" t="n"/>
+      <c r="I21" s="366" t="n"/>
+      <c r="J21" s="366" t="n"/>
+      <c r="K21" s="366" t="n"/>
+      <c r="L21" s="366" t="n"/>
+      <c r="M21" s="366" t="n"/>
       <c r="N21" s="176">
         <f>IF(COUNT(B21:M21)=0,"",SUM(B21:M21))</f>
         <v/>
       </c>
-      <c r="O21" s="126" t="n"/>
-      <c r="P21" s="89" t="n"/>
+      <c r="O21" s="366" t="n"/>
+      <c r="P21" s="362" t="n"/>
     </row>
     <row r="22" ht="16.95" customHeight="1" s="127">
-      <c r="A22" s="52" t="inlineStr">
+      <c r="A22" s="365" t="inlineStr">
         <is>
           <t>Casos antiguos de enfermedad laboral</t>
         </is>
       </c>
-      <c r="B22" s="126" t="n"/>
-      <c r="C22" s="126" t="n"/>
-      <c r="D22" s="126" t="n"/>
-      <c r="E22" s="126" t="n"/>
-      <c r="F22" s="126" t="n"/>
-      <c r="G22" s="126" t="n"/>
-      <c r="H22" s="126" t="n"/>
-      <c r="I22" s="126" t="n"/>
-      <c r="J22" s="126" t="n"/>
-      <c r="K22" s="126" t="n"/>
-      <c r="L22" s="126" t="n"/>
-      <c r="M22" s="126" t="n"/>
+      <c r="B22" s="366" t="n"/>
+      <c r="C22" s="366" t="n"/>
+      <c r="D22" s="366" t="n"/>
+      <c r="E22" s="366" t="n"/>
+      <c r="F22" s="366" t="n"/>
+      <c r="G22" s="366" t="n"/>
+      <c r="H22" s="366" t="n"/>
+      <c r="I22" s="366" t="n"/>
+      <c r="J22" s="366" t="n"/>
+      <c r="K22" s="366" t="n"/>
+      <c r="L22" s="366" t="n"/>
+      <c r="M22" s="366" t="n"/>
       <c r="N22" s="176">
         <f>IF(COUNT(B22:M22)=0,"",SUM(B22:M22))</f>
         <v/>
       </c>
-      <c r="O22" s="126" t="n"/>
-      <c r="P22" s="89" t="n"/>
+      <c r="O22" s="366" t="n"/>
+      <c r="P22" s="362" t="n"/>
     </row>
     <row r="23" ht="16.95" customHeight="1" s="127">
-      <c r="A23" s="52" t="inlineStr">
+      <c r="A23" s="365" t="inlineStr">
         <is>
           <t>Incidentes y casi accidentes</t>
         </is>
       </c>
-      <c r="B23" s="126" t="n"/>
-      <c r="C23" s="126" t="n"/>
-      <c r="D23" s="126" t="n"/>
-      <c r="E23" s="126" t="n"/>
-      <c r="F23" s="126" t="n"/>
-      <c r="G23" s="126" t="n"/>
-      <c r="H23" s="126" t="n"/>
-      <c r="I23" s="126" t="n"/>
-      <c r="J23" s="126" t="n"/>
-      <c r="K23" s="126" t="n"/>
-      <c r="L23" s="126" t="n"/>
-      <c r="M23" s="126" t="n"/>
+      <c r="B23" s="366" t="n"/>
+      <c r="C23" s="366" t="n"/>
+      <c r="D23" s="366" t="n"/>
+      <c r="E23" s="366" t="n"/>
+      <c r="F23" s="366" t="n"/>
+      <c r="G23" s="366" t="n"/>
+      <c r="H23" s="366" t="n"/>
+      <c r="I23" s="366" t="n"/>
+      <c r="J23" s="366" t="n"/>
+      <c r="K23" s="366" t="n"/>
+      <c r="L23" s="366" t="n"/>
+      <c r="M23" s="366" t="n"/>
       <c r="N23" s="176">
         <f>IF(COUNT(B23:M23)=0,"",SUM(B23:M23))</f>
         <v/>
       </c>
-      <c r="O23" s="126" t="n"/>
-      <c r="P23" s="89" t="n"/>
+      <c r="O23" s="366" t="n"/>
+      <c r="P23" s="362" t="n"/>
     </row>
     <row r="24" ht="16.95" customHeight="1" s="127">
-      <c r="A24" s="52" t="inlineStr">
+      <c r="A24" s="365" t="inlineStr">
         <is>
           <t>Días de ausencia por incapacidad médica</t>
         </is>
       </c>
-      <c r="B24" s="126" t="n"/>
-      <c r="C24" s="126" t="n"/>
-      <c r="D24" s="126" t="n"/>
-      <c r="E24" s="126" t="n"/>
-      <c r="F24" s="126" t="n"/>
-      <c r="G24" s="126" t="n"/>
-      <c r="H24" s="126" t="n"/>
-      <c r="I24" s="126" t="n"/>
-      <c r="J24" s="126" t="n"/>
-      <c r="K24" s="126" t="n"/>
-      <c r="L24" s="126" t="n"/>
-      <c r="M24" s="126" t="n"/>
+      <c r="B24" s="366" t="n"/>
+      <c r="C24" s="366" t="n"/>
+      <c r="D24" s="366" t="n"/>
+      <c r="E24" s="366" t="n"/>
+      <c r="F24" s="366" t="n"/>
+      <c r="G24" s="366" t="n"/>
+      <c r="H24" s="366" t="n"/>
+      <c r="I24" s="366" t="n"/>
+      <c r="J24" s="366" t="n"/>
+      <c r="K24" s="366" t="n"/>
+      <c r="L24" s="366" t="n"/>
+      <c r="M24" s="366" t="n"/>
       <c r="N24" s="176">
         <f>IF(COUNT(B24:M24)=0,"",SUM(B24:M24))</f>
         <v/>
       </c>
-      <c r="O24" s="126" t="n"/>
-      <c r="P24" s="89" t="n"/>
+      <c r="O24" s="366" t="n"/>
+      <c r="P24" s="362" t="n"/>
     </row>
     <row r="25" ht="16.95" customHeight="1" s="127">
-      <c r="A25" s="52" t="inlineStr">
+      <c r="A25" s="365" t="inlineStr">
         <is>
           <t>Días de trabajo programados</t>
         </is>
       </c>
-      <c r="B25" s="126" t="n"/>
-      <c r="C25" s="126" t="n"/>
-      <c r="D25" s="126" t="n"/>
-      <c r="E25" s="126" t="n"/>
-      <c r="F25" s="126" t="n"/>
-      <c r="G25" s="126" t="n"/>
-      <c r="H25" s="126" t="n"/>
-      <c r="I25" s="126" t="n"/>
-      <c r="J25" s="126" t="n"/>
-      <c r="K25" s="126" t="n"/>
-      <c r="L25" s="126" t="n"/>
-      <c r="M25" s="126" t="n"/>
+      <c r="B25" s="366" t="n"/>
+      <c r="C25" s="366" t="n"/>
+      <c r="D25" s="366" t="n"/>
+      <c r="E25" s="366" t="n"/>
+      <c r="F25" s="366" t="n"/>
+      <c r="G25" s="366" t="n"/>
+      <c r="H25" s="366" t="n"/>
+      <c r="I25" s="366" t="n"/>
+      <c r="J25" s="366" t="n"/>
+      <c r="K25" s="366" t="n"/>
+      <c r="L25" s="366" t="n"/>
+      <c r="M25" s="366" t="n"/>
       <c r="N25" s="176">
         <f>IF(COUNT(B25:M25)=0,"",SUM(B25:M25))</f>
         <v/>
       </c>
-      <c r="O25" s="126" t="n"/>
-      <c r="P25" s="89" t="n"/>
+      <c r="O25" s="366" t="n"/>
+      <c r="P25" s="362" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="127">
       <c r="A26" s="137" t="inlineStr">
@@ -3105,7 +3182,7 @@
       <c r="P27" s="89" t="n"/>
     </row>
     <row r="28" ht="16.95" customHeight="1" s="127">
-      <c r="A28" s="52" t="inlineStr">
+      <c r="A28" s="365" t="inlineStr">
         <is>
           <t>Frecuencia de accidentalidad (%)</t>
         </is>
@@ -3162,11 +3239,11 @@
         <f>IFERROR(IF(OR(N15="",N15=0,N17=""),"",N17/N15*100),"")</f>
         <v/>
       </c>
-      <c r="O28" s="126" t="n"/>
-      <c r="P28" s="89" t="n"/>
+      <c r="O28" s="366" t="n"/>
+      <c r="P28" s="362" t="n"/>
     </row>
     <row r="29" ht="16.95" customHeight="1" s="127">
-      <c r="A29" s="52" t="inlineStr">
+      <c r="A29" s="365" t="inlineStr">
         <is>
           <t>Severidad de accidentalidad (%)</t>
         </is>
@@ -3223,11 +3300,11 @@
         <f>IFERROR(IF(OR(N15="",N15=0,N19=""),"",N19/N15*100),"")</f>
         <v/>
       </c>
-      <c r="O29" s="126" t="n"/>
-      <c r="P29" s="89" t="n"/>
+      <c r="O29" s="366" t="n"/>
+      <c r="P29" s="362" t="n"/>
     </row>
     <row r="30" ht="16.95" customHeight="1" s="127">
-      <c r="A30" s="52" t="inlineStr">
+      <c r="A30" s="365" t="inlineStr">
         <is>
           <t>Proporción de AT mortales (%)</t>
         </is>
@@ -3284,11 +3361,11 @@
         <f>IFERROR(IF(OR(N17="",N17=0,N20=""),"",N20/N17*100),"")</f>
         <v/>
       </c>
-      <c r="O30" s="126" t="n"/>
-      <c r="P30" s="89" t="n"/>
-    </row>
-    <row r="31" ht="16.95" customHeight="1" s="127">
-      <c r="A31" s="52" t="inlineStr">
+      <c r="O30" s="366" t="n"/>
+      <c r="P30" s="362" t="n"/>
+    </row>
+    <row r="31" ht="29" customHeight="1" s="127">
+      <c r="A31" s="365" t="inlineStr">
         <is>
           <t>Incidencia de enfermedad laboral (por 100.000)</t>
         </is>
@@ -3345,11 +3422,11 @@
         <f>IFERROR(IF(OR(N15="",N15=0,N21=""),"",N21/N15*100000),"")</f>
         <v/>
       </c>
-      <c r="O31" s="126" t="n"/>
-      <c r="P31" s="89" t="n"/>
-    </row>
-    <row r="32" ht="16.95" customHeight="1" s="127">
-      <c r="A32" s="52" t="inlineStr">
+      <c r="O31" s="366" t="n"/>
+      <c r="P31" s="362" t="n"/>
+    </row>
+    <row r="32" ht="29" customHeight="1" s="127">
+      <c r="A32" s="365" t="inlineStr">
         <is>
           <t>Prevalencia de enfermedad laboral (por 100.000)</t>
         </is>
@@ -3406,11 +3483,11 @@
         <f>IFERROR(IF(OR(N15="",N15=0,AND(N21="",N22="")),"",(N21+N22)/N15*100000),"")</f>
         <v/>
       </c>
-      <c r="O32" s="126" t="n"/>
-      <c r="P32" s="89" t="n"/>
+      <c r="O32" s="366" t="n"/>
+      <c r="P32" s="362" t="n"/>
     </row>
     <row r="33" ht="16.95" customHeight="1" s="127">
-      <c r="A33" s="52" t="inlineStr">
+      <c r="A33" s="365" t="inlineStr">
         <is>
           <t>Ausentismo por causa médica (%)</t>
         </is>
@@ -3467,11 +3544,11 @@
         <f>IFERROR(IF(OR(N25="",N25=0,N24=""),"",N24/N25*100),"")</f>
         <v/>
       </c>
-      <c r="O33" s="126" t="n"/>
-      <c r="P33" s="89" t="n"/>
-    </row>
-    <row r="34" ht="16.95" customHeight="1" s="127">
-      <c r="A34" s="52" t="inlineStr">
+      <c r="O33" s="366" t="n"/>
+      <c r="P33" s="362" t="n"/>
+    </row>
+    <row r="34" ht="29" customHeight="1" s="127">
+      <c r="A34" s="365" t="inlineStr">
         <is>
           <t>Índice de frecuencia, IF (AT × 240.000 ÷ HHT)</t>
         </is>
@@ -3528,11 +3605,11 @@
         <f>IFERROR(IF(OR(N16="",N16=0,N17=""),"",N17*240000/N16),"")</f>
         <v/>
       </c>
-      <c r="O34" s="126" t="n"/>
-      <c r="P34" s="89" t="n"/>
-    </row>
-    <row r="35" ht="16.95" customHeight="1" s="127">
-      <c r="A35" s="52" t="inlineStr">
+      <c r="O34" s="366" t="n"/>
+      <c r="P34" s="362" t="n"/>
+    </row>
+    <row r="35" ht="29" customHeight="1" s="127">
+      <c r="A35" s="365" t="inlineStr">
         <is>
           <t>Índice de severidad, IS (días × 240.000 ÷ HHT)</t>
         </is>
@@ -3589,11 +3666,11 @@
         <f>IFERROR(IF(OR(N16="",N16=0,N19=""),"",N19*240000/N16),"")</f>
         <v/>
       </c>
-      <c r="O35" s="126" t="n"/>
-      <c r="P35" s="89" t="n"/>
-    </row>
-    <row r="36" ht="16.95" customHeight="1" s="127">
-      <c r="A36" s="331" t="inlineStr">
+      <c r="O35" s="366" t="n"/>
+      <c r="P35" s="362" t="n"/>
+    </row>
+    <row r="36" ht="29" customHeight="1" s="127">
+      <c r="A36" s="367" t="inlineStr">
         <is>
           <t>Índice de lesiones incapacitantes, ILI (IF × IS ÷ 1.000)</t>
         </is>
@@ -3650,8 +3727,8 @@
         <f>IFERROR(IF(OR(N34="",N35=""),"",N34*N35/1000),"")</f>
         <v/>
       </c>
-      <c r="O36" s="337" t="n"/>
-      <c r="P36" s="94" t="n"/>
+      <c r="O36" s="368" t="n"/>
+      <c r="P36" s="369" t="n"/>
     </row>
     <row r="37" ht="16.05" customHeight="1" s="127">
       <c r="A37" s="255" t="inlineStr">
@@ -3776,57 +3853,57 @@
       <c r="P39" s="89" t="n"/>
     </row>
     <row r="40" ht="16.95" customHeight="1" s="127">
-      <c r="A40" s="52" t="inlineStr">
+      <c r="A40" s="365" t="inlineStr">
         <is>
           <t>Capacitaciones programadas</t>
         </is>
       </c>
-      <c r="B40" s="126" t="n"/>
-      <c r="C40" s="126" t="n"/>
-      <c r="D40" s="126" t="n"/>
-      <c r="E40" s="126" t="n"/>
-      <c r="F40" s="126" t="n"/>
-      <c r="G40" s="126" t="n"/>
-      <c r="H40" s="126" t="n"/>
-      <c r="I40" s="126" t="n"/>
-      <c r="J40" s="126" t="n"/>
-      <c r="K40" s="126" t="n"/>
-      <c r="L40" s="126" t="n"/>
-      <c r="M40" s="126" t="n"/>
+      <c r="B40" s="366" t="n"/>
+      <c r="C40" s="366" t="n"/>
+      <c r="D40" s="366" t="n"/>
+      <c r="E40" s="366" t="n"/>
+      <c r="F40" s="366" t="n"/>
+      <c r="G40" s="366" t="n"/>
+      <c r="H40" s="366" t="n"/>
+      <c r="I40" s="366" t="n"/>
+      <c r="J40" s="366" t="n"/>
+      <c r="K40" s="366" t="n"/>
+      <c r="L40" s="366" t="n"/>
+      <c r="M40" s="366" t="n"/>
       <c r="N40" s="176">
         <f>IF(COUNT(B40:M40)=0,"",SUM(B40:M40))</f>
         <v/>
       </c>
-      <c r="O40" s="126" t="n"/>
-      <c r="P40" s="89" t="n"/>
+      <c r="O40" s="366" t="n"/>
+      <c r="P40" s="362" t="n"/>
     </row>
     <row r="41" ht="16.95" customHeight="1" s="127">
-      <c r="A41" s="52" t="inlineStr">
+      <c r="A41" s="365" t="inlineStr">
         <is>
           <t>Capacitaciones ejecutadas</t>
         </is>
       </c>
-      <c r="B41" s="126" t="n"/>
-      <c r="C41" s="126" t="n"/>
-      <c r="D41" s="126" t="n"/>
-      <c r="E41" s="126" t="n"/>
-      <c r="F41" s="126" t="n"/>
-      <c r="G41" s="126" t="n"/>
-      <c r="H41" s="126" t="n"/>
-      <c r="I41" s="126" t="n"/>
-      <c r="J41" s="126" t="n"/>
-      <c r="K41" s="126" t="n"/>
-      <c r="L41" s="126" t="n"/>
-      <c r="M41" s="126" t="n"/>
+      <c r="B41" s="366" t="n"/>
+      <c r="C41" s="366" t="n"/>
+      <c r="D41" s="366" t="n"/>
+      <c r="E41" s="366" t="n"/>
+      <c r="F41" s="366" t="n"/>
+      <c r="G41" s="366" t="n"/>
+      <c r="H41" s="366" t="n"/>
+      <c r="I41" s="366" t="n"/>
+      <c r="J41" s="366" t="n"/>
+      <c r="K41" s="366" t="n"/>
+      <c r="L41" s="366" t="n"/>
+      <c r="M41" s="366" t="n"/>
       <c r="N41" s="176">
         <f>IF(COUNT(B41:M41)=0,"",SUM(B41:M41))</f>
         <v/>
       </c>
-      <c r="O41" s="126" t="n"/>
-      <c r="P41" s="89" t="n"/>
+      <c r="O41" s="366" t="n"/>
+      <c r="P41" s="362" t="n"/>
     </row>
     <row r="42" ht="16.95" customHeight="1" s="127">
-      <c r="A42" s="54" t="inlineStr">
+      <c r="A42" s="370" t="inlineStr">
         <is>
           <t>Cumplimiento del plan de capacitación (%)</t>
         </is>
@@ -3883,61 +3960,61 @@
         <f>IFERROR(IF(OR(N40="",N40=0,N41=""),"",N41/N40),"")</f>
         <v/>
       </c>
-      <c r="O42" s="126" t="n"/>
-      <c r="P42" s="89" t="n"/>
+      <c r="O42" s="366" t="n"/>
+      <c r="P42" s="362" t="n"/>
     </row>
     <row r="43" ht="16.95" customHeight="1" s="127">
-      <c r="A43" s="52" t="inlineStr">
+      <c r="A43" s="365" t="inlineStr">
         <is>
           <t>Inspecciones programadas</t>
         </is>
       </c>
-      <c r="B43" s="126" t="n"/>
-      <c r="C43" s="126" t="n"/>
-      <c r="D43" s="126" t="n"/>
-      <c r="E43" s="126" t="n"/>
-      <c r="F43" s="126" t="n"/>
-      <c r="G43" s="126" t="n"/>
-      <c r="H43" s="126" t="n"/>
-      <c r="I43" s="126" t="n"/>
-      <c r="J43" s="126" t="n"/>
-      <c r="K43" s="126" t="n"/>
-      <c r="L43" s="126" t="n"/>
-      <c r="M43" s="126" t="n"/>
+      <c r="B43" s="366" t="n"/>
+      <c r="C43" s="366" t="n"/>
+      <c r="D43" s="366" t="n"/>
+      <c r="E43" s="366" t="n"/>
+      <c r="F43" s="366" t="n"/>
+      <c r="G43" s="366" t="n"/>
+      <c r="H43" s="366" t="n"/>
+      <c r="I43" s="366" t="n"/>
+      <c r="J43" s="366" t="n"/>
+      <c r="K43" s="366" t="n"/>
+      <c r="L43" s="366" t="n"/>
+      <c r="M43" s="366" t="n"/>
       <c r="N43" s="176">
         <f>IF(COUNT(B43:M43)=0,"",SUM(B43:M43))</f>
         <v/>
       </c>
-      <c r="O43" s="126" t="n"/>
-      <c r="P43" s="89" t="n"/>
+      <c r="O43" s="366" t="n"/>
+      <c r="P43" s="362" t="n"/>
     </row>
     <row r="44" ht="16.95" customHeight="1" s="127">
-      <c r="A44" s="52" t="inlineStr">
+      <c r="A44" s="365" t="inlineStr">
         <is>
           <t>Inspecciones ejecutadas</t>
         </is>
       </c>
-      <c r="B44" s="126" t="n"/>
-      <c r="C44" s="126" t="n"/>
-      <c r="D44" s="126" t="n"/>
-      <c r="E44" s="126" t="n"/>
-      <c r="F44" s="126" t="n"/>
-      <c r="G44" s="126" t="n"/>
-      <c r="H44" s="126" t="n"/>
-      <c r="I44" s="126" t="n"/>
-      <c r="J44" s="126" t="n"/>
-      <c r="K44" s="126" t="n"/>
-      <c r="L44" s="126" t="n"/>
-      <c r="M44" s="126" t="n"/>
+      <c r="B44" s="366" t="n"/>
+      <c r="C44" s="366" t="n"/>
+      <c r="D44" s="366" t="n"/>
+      <c r="E44" s="366" t="n"/>
+      <c r="F44" s="366" t="n"/>
+      <c r="G44" s="366" t="n"/>
+      <c r="H44" s="366" t="n"/>
+      <c r="I44" s="366" t="n"/>
+      <c r="J44" s="366" t="n"/>
+      <c r="K44" s="366" t="n"/>
+      <c r="L44" s="366" t="n"/>
+      <c r="M44" s="366" t="n"/>
       <c r="N44" s="176">
         <f>IF(COUNT(B44:M44)=0,"",SUM(B44:M44))</f>
         <v/>
       </c>
-      <c r="O44" s="126" t="n"/>
-      <c r="P44" s="89" t="n"/>
+      <c r="O44" s="366" t="n"/>
+      <c r="P44" s="362" t="n"/>
     </row>
     <row r="45" ht="16.95" customHeight="1" s="127">
-      <c r="A45" s="54" t="inlineStr">
+      <c r="A45" s="370" t="inlineStr">
         <is>
           <t>Cumplimiento del plan de inspecciones (%)</t>
         </is>
@@ -3994,61 +4071,61 @@
         <f>IFERROR(IF(OR(N43="",N43=0,N44=""),"",N44/N43),"")</f>
         <v/>
       </c>
-      <c r="O45" s="126" t="n"/>
-      <c r="P45" s="89" t="n"/>
+      <c r="O45" s="366" t="n"/>
+      <c r="P45" s="362" t="n"/>
     </row>
     <row r="46" ht="16.95" customHeight="1" s="127">
-      <c r="A46" s="52" t="inlineStr">
+      <c r="A46" s="365" t="inlineStr">
         <is>
           <t>Acciones correctivas abiertas en el mes</t>
         </is>
       </c>
-      <c r="B46" s="126" t="n"/>
-      <c r="C46" s="126" t="n"/>
-      <c r="D46" s="126" t="n"/>
-      <c r="E46" s="126" t="n"/>
-      <c r="F46" s="126" t="n"/>
-      <c r="G46" s="126" t="n"/>
-      <c r="H46" s="126" t="n"/>
-      <c r="I46" s="126" t="n"/>
-      <c r="J46" s="126" t="n"/>
-      <c r="K46" s="126" t="n"/>
-      <c r="L46" s="126" t="n"/>
-      <c r="M46" s="126" t="n"/>
+      <c r="B46" s="366" t="n"/>
+      <c r="C46" s="366" t="n"/>
+      <c r="D46" s="366" t="n"/>
+      <c r="E46" s="366" t="n"/>
+      <c r="F46" s="366" t="n"/>
+      <c r="G46" s="366" t="n"/>
+      <c r="H46" s="366" t="n"/>
+      <c r="I46" s="366" t="n"/>
+      <c r="J46" s="366" t="n"/>
+      <c r="K46" s="366" t="n"/>
+      <c r="L46" s="366" t="n"/>
+      <c r="M46" s="366" t="n"/>
       <c r="N46" s="176">
         <f>IF(COUNT(B46:M46)=0,"",SUM(B46:M46))</f>
         <v/>
       </c>
-      <c r="O46" s="126" t="n"/>
-      <c r="P46" s="89" t="n"/>
+      <c r="O46" s="366" t="n"/>
+      <c r="P46" s="362" t="n"/>
     </row>
     <row r="47" ht="16.95" customHeight="1" s="127">
-      <c r="A47" s="52" t="inlineStr">
+      <c r="A47" s="365" t="inlineStr">
         <is>
           <t>Acciones correctivas cerradas en el mes</t>
         </is>
       </c>
-      <c r="B47" s="126" t="n"/>
-      <c r="C47" s="126" t="n"/>
-      <c r="D47" s="126" t="n"/>
-      <c r="E47" s="126" t="n"/>
-      <c r="F47" s="126" t="n"/>
-      <c r="G47" s="126" t="n"/>
-      <c r="H47" s="126" t="n"/>
-      <c r="I47" s="126" t="n"/>
-      <c r="J47" s="126" t="n"/>
-      <c r="K47" s="126" t="n"/>
-      <c r="L47" s="126" t="n"/>
-      <c r="M47" s="126" t="n"/>
+      <c r="B47" s="366" t="n"/>
+      <c r="C47" s="366" t="n"/>
+      <c r="D47" s="366" t="n"/>
+      <c r="E47" s="366" t="n"/>
+      <c r="F47" s="366" t="n"/>
+      <c r="G47" s="366" t="n"/>
+      <c r="H47" s="366" t="n"/>
+      <c r="I47" s="366" t="n"/>
+      <c r="J47" s="366" t="n"/>
+      <c r="K47" s="366" t="n"/>
+      <c r="L47" s="366" t="n"/>
+      <c r="M47" s="366" t="n"/>
       <c r="N47" s="176">
         <f>IF(COUNT(B47:M47)=0,"",SUM(B47:M47))</f>
         <v/>
       </c>
-      <c r="O47" s="126" t="n"/>
-      <c r="P47" s="89" t="n"/>
+      <c r="O47" s="366" t="n"/>
+      <c r="P47" s="362" t="n"/>
     </row>
     <row r="48" ht="16.95" customHeight="1" s="127">
-      <c r="A48" s="54" t="inlineStr">
+      <c r="A48" s="370" t="inlineStr">
         <is>
           <t>Cierre de acciones correctivas (%)</t>
         </is>
@@ -4105,33 +4182,33 @@
         <f>IFERROR(IF(OR(N46="",N46=0,N47=""),"",N47/N46),"")</f>
         <v/>
       </c>
-      <c r="O48" s="126" t="n"/>
-      <c r="P48" s="89" t="n"/>
-    </row>
-    <row r="49" ht="16.95" customHeight="1" s="127">
-      <c r="A49" s="52" t="inlineStr">
+      <c r="O48" s="366" t="n"/>
+      <c r="P48" s="362" t="n"/>
+    </row>
+    <row r="49" ht="29" customHeight="1" s="127">
+      <c r="A49" s="365" t="inlineStr">
         <is>
           <t>Actos y condiciones inseguras reportados (N°)</t>
         </is>
       </c>
-      <c r="B49" s="126" t="n"/>
-      <c r="C49" s="126" t="n"/>
-      <c r="D49" s="126" t="n"/>
-      <c r="E49" s="126" t="n"/>
-      <c r="F49" s="126" t="n"/>
-      <c r="G49" s="126" t="n"/>
-      <c r="H49" s="126" t="n"/>
-      <c r="I49" s="126" t="n"/>
-      <c r="J49" s="126" t="n"/>
-      <c r="K49" s="126" t="n"/>
-      <c r="L49" s="126" t="n"/>
-      <c r="M49" s="126" t="n"/>
+      <c r="B49" s="366" t="n"/>
+      <c r="C49" s="366" t="n"/>
+      <c r="D49" s="366" t="n"/>
+      <c r="E49" s="366" t="n"/>
+      <c r="F49" s="366" t="n"/>
+      <c r="G49" s="366" t="n"/>
+      <c r="H49" s="366" t="n"/>
+      <c r="I49" s="366" t="n"/>
+      <c r="J49" s="366" t="n"/>
+      <c r="K49" s="366" t="n"/>
+      <c r="L49" s="366" t="n"/>
+      <c r="M49" s="366" t="n"/>
       <c r="N49" s="176">
         <f>IF(COUNT(B49:M49)=0,"",SUM(B49:M49))</f>
         <v/>
       </c>
-      <c r="O49" s="126" t="n"/>
-      <c r="P49" s="89" t="n"/>
+      <c r="O49" s="366" t="n"/>
+      <c r="P49" s="362" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="127">
       <c r="A50" s="137" t="inlineStr">
@@ -4156,52 +4233,94 @@
       <c r="P50" s="97" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1" s="127">
-      <c r="A51" s="100" t="n"/>
-      <c r="B51" s="104" t="n"/>
-      <c r="C51" s="104" t="n"/>
-      <c r="D51" s="104" t="n"/>
-      <c r="E51" s="104" t="n"/>
-      <c r="F51" s="104" t="n"/>
-      <c r="G51" s="104" t="n"/>
-      <c r="H51" s="104" t="n"/>
-      <c r="I51" s="104" t="n"/>
-      <c r="J51" s="104" t="n"/>
-      <c r="K51" s="104" t="n"/>
-      <c r="L51" s="104" t="n"/>
-      <c r="M51" s="104" t="n"/>
-      <c r="N51" s="104" t="n"/>
-      <c r="O51" s="104" t="n"/>
-      <c r="P51" s="94" t="n"/>
+      <c r="A51" s="371" t="n"/>
+      <c r="B51" s="372" t="n"/>
+      <c r="C51" s="372" t="n"/>
+      <c r="D51" s="372" t="n"/>
+      <c r="E51" s="372" t="n"/>
+      <c r="F51" s="372" t="n"/>
+      <c r="G51" s="372" t="n"/>
+      <c r="H51" s="372" t="n"/>
+      <c r="I51" s="372" t="n"/>
+      <c r="J51" s="372" t="n"/>
+      <c r="K51" s="372" t="n"/>
+      <c r="L51" s="372" t="n"/>
+      <c r="M51" s="372" t="n"/>
+      <c r="N51" s="372" t="n"/>
+      <c r="O51" s="372" t="n"/>
+      <c r="P51" s="369" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1" s="127">
-      <c r="A52" s="95" t="n"/>
-      <c r="P52" s="92" t="n"/>
+      <c r="A52" s="373" t="n"/>
+      <c r="B52" s="374" t="n"/>
+      <c r="C52" s="374" t="n"/>
+      <c r="D52" s="374" t="n"/>
+      <c r="E52" s="374" t="n"/>
+      <c r="F52" s="374" t="n"/>
+      <c r="G52" s="374" t="n"/>
+      <c r="H52" s="374" t="n"/>
+      <c r="I52" s="374" t="n"/>
+      <c r="J52" s="374" t="n"/>
+      <c r="K52" s="374" t="n"/>
+      <c r="L52" s="374" t="n"/>
+      <c r="M52" s="374" t="n"/>
+      <c r="N52" s="374" t="n"/>
+      <c r="O52" s="374" t="n"/>
+      <c r="P52" s="375" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1" s="127">
-      <c r="A53" s="95" t="n"/>
-      <c r="P53" s="92" t="n"/>
+      <c r="A53" s="373" t="n"/>
+      <c r="B53" s="374" t="n"/>
+      <c r="C53" s="374" t="n"/>
+      <c r="D53" s="374" t="n"/>
+      <c r="E53" s="374" t="n"/>
+      <c r="F53" s="374" t="n"/>
+      <c r="G53" s="374" t="n"/>
+      <c r="H53" s="374" t="n"/>
+      <c r="I53" s="374" t="n"/>
+      <c r="J53" s="374" t="n"/>
+      <c r="K53" s="374" t="n"/>
+      <c r="L53" s="374" t="n"/>
+      <c r="M53" s="374" t="n"/>
+      <c r="N53" s="374" t="n"/>
+      <c r="O53" s="374" t="n"/>
+      <c r="P53" s="375" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1" s="127">
-      <c r="A54" s="95" t="n"/>
-      <c r="P54" s="92" t="n"/>
+      <c r="A54" s="373" t="n"/>
+      <c r="B54" s="374" t="n"/>
+      <c r="C54" s="374" t="n"/>
+      <c r="D54" s="374" t="n"/>
+      <c r="E54" s="374" t="n"/>
+      <c r="F54" s="374" t="n"/>
+      <c r="G54" s="374" t="n"/>
+      <c r="H54" s="374" t="n"/>
+      <c r="I54" s="374" t="n"/>
+      <c r="J54" s="374" t="n"/>
+      <c r="K54" s="374" t="n"/>
+      <c r="L54" s="374" t="n"/>
+      <c r="M54" s="374" t="n"/>
+      <c r="N54" s="374" t="n"/>
+      <c r="O54" s="374" t="n"/>
+      <c r="P54" s="375" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1" s="127">
-      <c r="A55" s="96" t="n"/>
-      <c r="B55" s="98" t="n"/>
-      <c r="C55" s="98" t="n"/>
-      <c r="D55" s="98" t="n"/>
-      <c r="E55" s="98" t="n"/>
-      <c r="F55" s="98" t="n"/>
-      <c r="G55" s="98" t="n"/>
-      <c r="H55" s="98" t="n"/>
-      <c r="I55" s="98" t="n"/>
-      <c r="J55" s="98" t="n"/>
-      <c r="K55" s="98" t="n"/>
-      <c r="L55" s="98" t="n"/>
-      <c r="M55" s="98" t="n"/>
-      <c r="N55" s="98" t="n"/>
-      <c r="O55" s="98" t="n"/>
-      <c r="P55" s="97" t="n"/>
+      <c r="A55" s="376" t="n"/>
+      <c r="B55" s="377" t="n"/>
+      <c r="C55" s="377" t="n"/>
+      <c r="D55" s="377" t="n"/>
+      <c r="E55" s="377" t="n"/>
+      <c r="F55" s="377" t="n"/>
+      <c r="G55" s="377" t="n"/>
+      <c r="H55" s="377" t="n"/>
+      <c r="I55" s="377" t="n"/>
+      <c r="J55" s="377" t="n"/>
+      <c r="K55" s="377" t="n"/>
+      <c r="L55" s="377" t="n"/>
+      <c r="M55" s="377" t="n"/>
+      <c r="N55" s="377" t="n"/>
+      <c r="O55" s="377" t="n"/>
+      <c r="P55" s="378" t="n"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="127">
       <c r="A56" s="137" t="inlineStr">
@@ -4267,27 +4386,27 @@
         </is>
       </c>
       <c r="C58" s="97" t="n"/>
-      <c r="D58" s="301" t="n"/>
-      <c r="E58" s="97" t="n"/>
+      <c r="D58" s="379" t="n"/>
+      <c r="E58" s="378" t="n"/>
       <c r="F58" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="G58" s="97" t="n"/>
-      <c r="H58" s="301" t="n"/>
-      <c r="I58" s="98" t="n"/>
-      <c r="J58" s="97" t="n"/>
+      <c r="H58" s="379" t="n"/>
+      <c r="I58" s="377" t="n"/>
+      <c r="J58" s="378" t="n"/>
       <c r="K58" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="L58" s="97" t="n"/>
-      <c r="M58" s="301" t="n"/>
-      <c r="N58" s="98" t="n"/>
-      <c r="O58" s="98" t="n"/>
-      <c r="P58" s="97" t="n"/>
+      <c r="M58" s="379" t="n"/>
+      <c r="N58" s="377" t="n"/>
+      <c r="O58" s="377" t="n"/>
+      <c r="P58" s="378" t="n"/>
     </row>
     <row r="59" ht="21" customHeight="1" s="127">
       <c r="A59" s="131" t="n"/>
@@ -4297,27 +4416,27 @@
         </is>
       </c>
       <c r="C59" s="89" t="n"/>
-      <c r="D59" s="68" t="n"/>
-      <c r="E59" s="89" t="n"/>
+      <c r="D59" s="364" t="n"/>
+      <c r="E59" s="362" t="n"/>
       <c r="F59" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="G59" s="89" t="n"/>
-      <c r="H59" s="68" t="n"/>
-      <c r="I59" s="93" t="n"/>
-      <c r="J59" s="89" t="n"/>
+      <c r="H59" s="364" t="n"/>
+      <c r="I59" s="361" t="n"/>
+      <c r="J59" s="362" t="n"/>
       <c r="K59" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="L59" s="89" t="n"/>
-      <c r="M59" s="68" t="n"/>
-      <c r="N59" s="93" t="n"/>
-      <c r="O59" s="93" t="n"/>
-      <c r="P59" s="89" t="n"/>
+      <c r="M59" s="364" t="n"/>
+      <c r="N59" s="361" t="n"/>
+      <c r="O59" s="361" t="n"/>
+      <c r="P59" s="362" t="n"/>
     </row>
     <row r="60" ht="21" customHeight="1" s="127">
       <c r="A60" s="132" t="n"/>
@@ -4327,27 +4446,27 @@
         </is>
       </c>
       <c r="C60" s="89" t="n"/>
-      <c r="D60" s="68" t="n"/>
-      <c r="E60" s="89" t="n"/>
+      <c r="D60" s="364" t="n"/>
+      <c r="E60" s="362" t="n"/>
       <c r="F60" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="G60" s="89" t="n"/>
-      <c r="H60" s="68" t="n"/>
-      <c r="I60" s="93" t="n"/>
-      <c r="J60" s="89" t="n"/>
+      <c r="H60" s="364" t="n"/>
+      <c r="I60" s="361" t="n"/>
+      <c r="J60" s="362" t="n"/>
       <c r="K60" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="L60" s="89" t="n"/>
-      <c r="M60" s="68" t="n"/>
-      <c r="N60" s="93" t="n"/>
-      <c r="O60" s="93" t="n"/>
-      <c r="P60" s="89" t="n"/>
+      <c r="M60" s="364" t="n"/>
+      <c r="N60" s="361" t="n"/>
+      <c r="O60" s="361" t="n"/>
+      <c r="P60" s="362" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="25" t="inlineStr">
@@ -4361,6 +4480,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="83">
     <mergeCell ref="O7:P7"/>
     <mergeCell ref="D60:E60"/>
